--- a/GearSage-client/rate/excel/line.xlsx
+++ b/GearSage-client/rate/excel/line.xlsx
@@ -457,7 +457,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H2" t="str">
-        <v>images/daiwa_lines/フィネス ブレイブ Z FINESSE BRAVE Z_FinesseBraveZ_4lb.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%95%E3%82%A3%E3%83%8D%E3%82%B9%20%E3%83%96%E3%83%AC%E3%82%A4%E3%83%96%20Z%20FINESSE%20BRAVE%20Z_FinesseBraveZ_4lb.jpg</v>
       </c>
       <c r="I2" t="str">
         <v/>
@@ -492,7 +492,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H3" t="str">
-        <v>images/daiwa_lines/BASS-Xフロロ 240 BASS-X FLUORO 240_BASS-X-FLUORO-240_8.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/BASS-X%E3%83%95%E3%83%AD%E3%83%AD%20240%20BASS-X%20FLUORO%20240_BASS-X-FLUORO-240_8.png</v>
       </c>
       <c r="I3" t="str">
         <v/>
@@ -527,7 +527,7 @@
         <v>PE</v>
       </c>
       <c r="H4" t="str">
-        <v>images/daiwa_lines/UVF タトゥーラ センサー×8＋Si2 UVF TATULA SENSOR×8+Si2_UVFTatulaSensor8-Si2.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E3%82%BF%E3%83%88%E3%82%A5%E3%83%BC%E3%83%A9%20%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC%C3%978%EF%BC%8BSi2%20UVF%20TATULA%20SENSOR%C3%978%2BSi2_UVFTatulaSensor8-Si2.jpg</v>
       </c>
       <c r="I4" t="str">
         <v/>
@@ -562,7 +562,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H5" t="str">
-        <v>images/daiwa_lines/スティーズ フロロ X’LINK STEEZ FLUORO X’LINK_SteezFluoroXLink.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%95%E3%83%AD%E3%83%AD%20X%E2%80%99LINK%20STEEZ%20FLUORO%20X%E2%80%99LINK_SteezFluoroXLink.jpg</v>
       </c>
       <c r="I5" t="str">
         <v/>
@@ -597,7 +597,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H6" t="str">
-        <v>images/daiwa_lines/モンスター ブレイブ Z MONSTER BRAVE Z_MonsterBraveZ_18lb.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%A2%E3%83%B3%E3%82%B9%E3%82%BF%E3%83%BC%20%E3%83%96%E3%83%AC%E3%82%A4%E3%83%96%20Z%20MONSTER%20BRAVE%20Z_MonsterBraveZ_18lb.jpg</v>
       </c>
       <c r="I6" t="str">
         <v/>
@@ -632,7 +632,7 @@
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>images/daiwa_lines/スティーズ デュラブラ マックス STEEZ DURABRA MAX_SteezDurabraMax.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%87%E3%83%A5%E3%83%A9%E3%83%96%E3%83%A9%20%E3%83%9E%E3%83%83%E3%82%AF%E3%82%B9%20STEEZ%20DURABRA%20MAX_SteezDurabraMax.jpg</v>
       </c>
       <c r="I7" t="str">
         <v/>
@@ -667,7 +667,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H8" t="str">
-        <v>images/daiwa_lines/バス-X フロロ BASS-X FLUORO_BASS-X100m_1.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%90%E3%82%B9-X%20%E3%83%95%E3%83%AD%E3%83%AD%20BASS-X%20FLUORO_BASS-X100m_1.jpg</v>
       </c>
       <c r="I8" t="str">
         <v/>
@@ -702,7 +702,7 @@
         <v>PE</v>
       </c>
       <c r="H9" t="str">
-        <v>images/daiwa_lines/UVF フロッグデュラセンサー×8＋Si2 UVF FROG DURA SENSOR×8+Si2_UVFFrogDuraSensor8PlusSi2.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E3%83%95%E3%83%AD%E3%83%83%E3%82%B0%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC%C3%978%EF%BC%8BSi2%20UVF%20FROG%20DURA%20SENSOR%C3%978%2BSi2_UVFFrogDuraSensor8PlusSi2.jpg</v>
       </c>
       <c r="I9" t="str">
         <v/>
@@ -737,7 +737,7 @@
         <v>Nylon</v>
       </c>
       <c r="H10" t="str">
-        <v>images/daiwa_lines/バス-X ナイロン BASS-X NYLON_BassXNylon.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%90%E3%82%B9-X%20%E3%83%8A%E3%82%A4%E3%83%AD%E3%83%B3%20BASS-X%20NYLON_BassXNylon.jpg</v>
       </c>
       <c r="I10" t="str">
         <v/>
@@ -772,7 +772,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H11" t="str">
-        <v>images/daiwa_lines/スティーズフロロ タフネス STEEZ FLUORO TOUGHNESS_STEEZ-FLUORO-TOUGHNESS.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%83%95%E3%83%AD%E3%83%AD%20%E3%82%BF%E3%83%95%E3%83%8D%E3%82%B9%20STEEZ%20FLUORO%20TOUGHNESS_STEEZ-FLUORO-TOUGHNESS.png</v>
       </c>
       <c r="I11" t="str">
         <v/>
@@ -807,7 +807,7 @@
         <v>Nylon</v>
       </c>
       <c r="H12" t="str">
-        <v>images/daiwa_lines/タトゥーラ タイプ ナイロン TATULA Type NYLON_TatulaTypeNylon.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%BF%E3%83%88%E3%82%A5%E3%83%BC%E3%83%A9%20%E3%82%BF%E3%82%A4%E3%83%97%20%E3%83%8A%E3%82%A4%E3%83%AD%E3%83%B3%20TATULA%20Type%20NYLON_TatulaTypeNylon.jpg</v>
       </c>
       <c r="I12" t="str">
         <v/>
@@ -842,7 +842,7 @@
         <v>Ester</v>
       </c>
       <c r="H13" t="str">
-        <v>images/daiwa_lines/プレッソエリアエステル TT PRESSO AREA ESTER TECHNICAL TUNE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%E3%82%A8%E3%83%AA%E3%82%A2%E3%82%A8%E3%82%B9%E3%83%86%E3%83%AB%20TT%20PRESSO%20AREA%20ESTER%20TECHNICAL%20TUNE_main.jpg</v>
       </c>
       <c r="I13" t="str">
         <v/>
@@ -877,7 +877,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H14" t="str">
-        <v>images/daiwa_lines/トラウトフロロリーダー TROUT FLUORO LEADER_TroutFluoroLeader_3lb.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%88%E3%83%A9%E3%82%A6%E3%83%88%E3%83%95%E3%83%AD%E3%83%AD%E3%83%AA%E3%83%BC%E3%83%80%E3%83%BC%20TROUT%20FLUORO%20LEADER_TroutFluoroLeader_3lb.jpg</v>
       </c>
       <c r="I14" t="str">
         <v/>
@@ -912,7 +912,7 @@
         <v>Nylon</v>
       </c>
       <c r="H15" t="str">
-        <v>images/daiwa_lines/プレッソエリアデュラブラMAX PRESSO AREA DURABRAMAX_main.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%E3%82%A8%E3%83%AA%E3%82%A2%E3%83%87%E3%83%A5%E3%83%A9%E3%83%96%E3%83%A9MAX%20PRESSO%20AREA%20DURABRAMAX_main.png</v>
       </c>
       <c r="I15" t="str">
         <v/>
@@ -947,7 +947,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H16" t="str">
-        <v>images/daiwa_lines/プレッソ　エリア　TYPE-F PRESSO AREA TYPE F_PressoAreaTypeF_100.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%E3%80%80%E3%82%A8%E3%83%AA%E3%82%A2%E3%80%80TYPE-F%20PRESSO%20AREA%20TYPE%20F_PressoAreaTypeF_100.jpg</v>
       </c>
       <c r="I16" t="str">
         <v/>
@@ -982,7 +982,7 @@
         <v/>
       </c>
       <c r="H17" t="str">
-        <v>images/daiwa_lines/プレッソ タイプN PRESSO TYPE N_PressoTypeN.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%82%BF%E3%82%A4%E3%83%97N%20PRESSO%20TYPE%20N_PressoTypeN.jpg</v>
       </c>
       <c r="I17" t="str">
         <v/>
@@ -1017,7 +1017,7 @@
         <v>PE</v>
       </c>
       <c r="H18" t="str">
-        <v>images/daiwa_lines/UVFプレッソエリアデュラセンサー×8EX+Si3 UVF PRESSO AREA DURA SENSOR X8EX+SI3_main.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%E3%82%A8%E3%83%AA%E3%82%A2%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC%C3%978EX%2BSi3%20UVF%20PRESSO%20AREA%20DURA%20SENSOR%20X8EX%2BSI3_main.png</v>
       </c>
       <c r="I18" t="str">
         <v/>
@@ -1052,7 +1052,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H19" t="str">
-        <v>images/daiwa_lines/月下美人フロロリーダー GEKKABIJIN FLUORO LEADER_GekkabijinFluoroLeader_Package1.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%E3%83%95%E3%83%AD%E3%83%AD%E3%83%AA%E3%83%BC%E3%83%80%E3%83%BC%20GEKKABIJIN%20FLUORO%20LEADER_GekkabijinFluoroLeader_Package1.jpg</v>
       </c>
       <c r="I19" t="str">
         <v/>
@@ -1087,7 +1087,7 @@
         <v>Ester</v>
       </c>
       <c r="H20" t="str">
-        <v>images/daiwa_lines/プレッソ エリア TYPE-E PRESSO AREA TYPE-E_PressoAreaTypeE.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%82%A8%E3%83%AA%E3%82%A2%20TYPE-E%20PRESSO%20AREA%20TYPE-E_PressoAreaTypeE.jpg</v>
       </c>
       <c r="I20" t="str">
         <v/>
@@ -1122,7 +1122,7 @@
         <v/>
       </c>
       <c r="H21" t="str">
-        <v>images/daiwa_lines/UVF エメラルダスデュラセンサーX8EX+Si3 IM UVF EMERALDAS DURASENSOR X8EX+SI3 IM_4550133628382.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E3%82%A8%E3%83%A1%E3%83%A9%E3%83%AB%E3%83%80%E3%82%B9%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BCX8EX%2BSi3%20IM%20UVF%20EMERALDAS%20DURASENSOR%20X8EX%2BSI3%20IM_4550133628382.jpg</v>
       </c>
       <c r="I21" t="str">
         <v/>
@@ -1157,7 +1157,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H22" t="str">
-        <v>images/daiwa_lines/紅牙フロロリーダーEX KOHGA FLUORO LEADER EX_KOHGA_FLUOROLEADER_EX_package_ol.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E7%B4%85%E7%89%99%E3%83%95%E3%83%AD%E3%83%AD%E3%83%AA%E3%83%BC%E3%83%80%E3%83%BCEX%20KOHGA%20FLUORO%20LEADER%20EX_KOHGA_FLUOROLEADER_EX_package_ol.png</v>
       </c>
       <c r="I22" t="str">
         <v/>
@@ -1192,7 +1192,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H23" t="str">
-        <v>images/daiwa_lines/フロロショックリーダーX FLUORO SHOCK LEADER X_FluoroShockLeaderX_Package.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%95%E3%83%AD%E3%83%AD%E3%82%B7%E3%83%A7%E3%83%83%E3%82%AF%E3%83%AA%E3%83%BC%E3%83%80%E3%83%BCX%20FLUORO%20SHOCK%20LEADER%20X_FluoroShockLeaderX_Package.jpg</v>
       </c>
       <c r="I23" t="str">
         <v/>
@@ -1227,7 +1227,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H24" t="str">
-        <v>images/daiwa_lines/モアザンリーダーEX II TYPE-F（フロロ） morethan LEADER EX II TYPE-F（FLUORO）_MT_LeaderType-F2_NaturalClear.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%A2%E3%82%A2%E3%82%B6%E3%83%B3%E3%83%AA%E3%83%BC%E3%83%80%E3%83%BCEX%20II%20TYPE-F%EF%BC%88%E3%83%95%E3%83%AD%E3%83%AD%EF%BC%89%20morethan%20LEADER%20EX%20II%20TYPE-F%EF%BC%88FLUORO%EF%BC%89_MT_LeaderType-F2_NaturalClear.jpg</v>
       </c>
       <c r="I24" t="str">
         <v/>
@@ -1262,7 +1262,7 @@
         <v>Nylon</v>
       </c>
       <c r="H25" t="str">
-        <v>images/daiwa_lines/シルバークリーク TYPE-N（ナイロン） SILVER CREEK TYPE-N_SilverCreekType-N.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%AF%E3%83%AA%E3%83%BC%E3%82%AF%20TYPE-N%EF%BC%88%E3%83%8A%E3%82%A4%E3%83%AD%E3%83%B3%EF%BC%89%20SILVER%20CREEK%20TYPE-N_SilverCreekType-N.jpg</v>
       </c>
       <c r="I25" t="str">
         <v/>
@@ -1297,7 +1297,7 @@
         <v/>
       </c>
       <c r="H26" t="str">
-        <v>images/daiwa_lines/UVF ソルティガデュラセンサー8＋Si2 UVF SALTIGA DURA SENSOR×8＋Si2_UVFSGDuraSensor8plusSi2.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E3%82%BD%E3%83%AB%E3%83%86%E3%82%A3%E3%82%AC%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC8%EF%BC%8BSi2%20UVF%20SALTIGA%20DURA%20SENSOR%C3%978%EF%BC%8BSi2_UVFSGDuraSensor8plusSi2.jpg</v>
       </c>
       <c r="I26" t="str">
         <v/>
@@ -1332,7 +1332,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H27" t="str">
-        <v>images/daiwa_lines/ソルティガ フロロリーダー X’LINK（クロスリンク） SALTIGA FLUORO LEADER X’LINK_SG_FuluroLaederXLink.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%BD%E3%83%AB%E3%83%86%E3%82%A3%E3%82%AC%20%E3%83%95%E3%83%AD%E3%83%AD%E3%83%AA%E3%83%BC%E3%83%80%E3%83%BC%20X%E2%80%99LINK%EF%BC%88%E3%82%AF%E3%83%AD%E3%82%B9%E3%83%AA%E3%83%B3%E3%82%AF%EF%BC%89%20SALTIGA%20FLUORO%20LEADER%20X%E2%80%99LINK_SG_FuluroLaederXLink.jpg</v>
       </c>
       <c r="I27" t="str">
         <v/>
@@ -1367,7 +1367,7 @@
         <v/>
       </c>
       <c r="H28" t="str">
-        <v>images/daiwa_lines/UVF ソルティガ SJ デュラセンサー×8＋Si2 UVF SALTIGA DURA SENSOR×8＋Si2_SGSJDURA8P.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E3%82%BD%E3%83%AB%E3%83%86%E3%82%A3%E3%82%AC%20SJ%20%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC%C3%978%EF%BC%8BSi2%20UVF%20SALTIGA%20DURA%20SENSOR%C3%978%EF%BC%8BSi2_SGSJDURA8P.jpg</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -1402,7 +1402,7 @@
         <v>Nylon</v>
       </c>
       <c r="H29" t="str">
-        <v>images/daiwa_lines/モアザンデュラブラ MAX MORETHAN DURABRA MAX_MORETHAN-DURABRA-MAX.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%A2%E3%82%A2%E3%82%B6%E3%83%B3%E3%83%87%E3%83%A5%E3%83%A9%E3%83%96%E3%83%A9%20MAX%20MORETHAN%20DURABRA%20MAX_MORETHAN-DURABRA-MAX.png</v>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -1437,7 +1437,7 @@
         <v>PE</v>
       </c>
       <c r="H30" t="str">
-        <v>images/daiwa_lines/UVF モアザン デュラセンサー×8＋Si² UVF MORETHAN DURASENSOR X8BRAID +Si²_UVF_MT_DuraSensor8BraidPlusSi2.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E3%83%A2%E3%82%A2%E3%82%B6%E3%83%B3%20%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC%C3%978%EF%BC%8BSi%C2%B2%20UVF%20MORETHAN%20DURASENSOR%20X8BRAID%20%2BSi%C2%B2_UVF_MT_DuraSensor8BraidPlusSi2.jpg</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -1472,7 +1472,7 @@
         <v>PE</v>
       </c>
       <c r="H31" t="str">
-        <v>images/daiwa_lines/UVF ソルティガデュラセンサー×12EX+Si3 UVF SALTIGA DURA SENSOR×12EX+Si3_SALTIGA-DURASENSOR-12EX.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E3%82%BD%E3%83%AB%E3%83%86%E3%82%A3%E3%82%AC%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC%C3%9712EX%2BSi3%20UVF%20SALTIGA%20DURA%20SENSOR%C3%9712EX%2BSi3_SALTIGA-DURASENSOR-12EX.jpg</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -1507,7 +1507,7 @@
         <v>PE</v>
       </c>
       <c r="H32" t="str">
-        <v>images/daiwa_lines/UVF月下美人デュラセンサー＋Si² UVF GEKKABIJIN DURA SENSOR＋Si²_UVFGekkabijinDuraSensorSi2.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC%EF%BC%8BSi%C2%B2%20UVF%20GEKKABIJIN%20DURA%20SENSOR%EF%BC%8BSi%C2%B2_UVFGekkabijinDuraSensorSi2.jpg</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -1542,7 +1542,7 @@
         <v>Nylon</v>
       </c>
       <c r="H33" t="str">
-        <v>images/daiwa_lines/ソルティガ ナイロンリーダー SALTIGA NYLON LEADER_SG_NylonLaeder40LB.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%BD%E3%83%AB%E3%83%86%E3%82%A3%E3%82%AC%20%E3%83%8A%E3%82%A4%E3%83%AD%E3%83%B3%E3%83%AA%E3%83%BC%E3%83%80%E3%83%BC%20SALTIGA%20NYLON%20LEADER_SG_NylonLaeder40LB.jpg</v>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -1577,7 +1577,7 @@
         <v/>
       </c>
       <c r="H34" t="str">
-        <v>images/daiwa_lines/月下美人TYPE-E 鋭感（エイカン） GEKKABIJIN TYPE-E EIKAN_GekkaTypeE_Eikan.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BATYPE-E%20%E9%8B%AD%E6%84%9F%EF%BC%88%E3%82%A8%E3%82%A4%E3%82%AB%E3%83%B3%EF%BC%89%20GEKKABIJIN%20TYPE-E%20EIKAN_GekkaTypeE_Eikan.jpg</v>
       </c>
       <c r="I34" t="str">
         <v/>
@@ -1647,7 +1647,7 @@
         <v/>
       </c>
       <c r="H36" t="str">
-        <v>images/daiwa_lines/エメラルダスオモリグリーダー EMERALDAS OMORIG LEADER_omorig-leader_4550133408427_data.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%A8%E3%83%A1%E3%83%A9%E3%83%AB%E3%83%80%E3%82%B9%E3%82%AA%E3%83%A2%E3%83%AA%E3%82%B0%E3%83%AA%E3%83%BC%E3%83%80%E3%83%BC%20EMERALDAS%20OMORIG%20LEADER_omorig-leader_4550133408427_data.jpg</v>
       </c>
       <c r="I36" t="str">
         <v/>
@@ -1682,7 +1682,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H37" t="str">
-        <v>images/daiwa_lines/HRF® ロックフィッシュフロロ HRF® ROCKFISH FLUORO_HRFRockFishFluoro.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/HRF%C2%AE%20%E3%83%AD%E3%83%83%E3%82%AF%E3%83%95%E3%82%A3%E3%83%83%E3%82%B7%E3%83%A5%E3%83%95%E3%83%AD%E3%83%AD%20HRF%C2%AE%20ROCKFISH%20FLUORO_HRFRockFishFluoro.jpg</v>
       </c>
       <c r="I37" t="str">
         <v/>
@@ -1717,7 +1717,7 @@
         <v>PE</v>
       </c>
       <c r="H38" t="str">
-        <v>images/daiwa_lines/UVF 紅牙 デュラセンサー×8＋Si2 UVF KOGA DURA SENSOR×8＋Si2_UVFKohgaDurasensor8Braid_1.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E7%B4%85%E7%89%99%20%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC%C3%978%EF%BC%8BSi2%20UVF%20KOGA%20DURA%20SENSOR%C3%978%EF%BC%8BSi2_UVFKohgaDurasensor8Braid_1.jpg</v>
       </c>
       <c r="I38" t="str">
         <v/>
@@ -1752,7 +1752,7 @@
         <v/>
       </c>
       <c r="H39" t="str">
-        <v>images/daiwa_lines/タチメタルEX SG TACHIMETAL EX SEAGREEN_TACHIMETAL-EX-SEAGREEN.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%BF%E3%83%81%E3%83%A1%E3%82%BF%E3%83%ABEX%20SG%20TACHIMETAL%20EX%20SEAGREEN_TACHIMETAL-EX-SEAGREEN.png</v>
       </c>
       <c r="I39" t="str">
         <v/>
@@ -1787,7 +1787,7 @@
         <v>PE</v>
       </c>
       <c r="H40" t="str">
-        <v>images/daiwa_lines/ベイトキャスティングデュラセンサー×12EX+Si3 BAIT CASTING DURA SENSOR X 12EX+SI3_BAIT_CASTING_DURA_SENSOR.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%99%E3%82%A4%E3%83%88%E3%82%AD%E3%83%A3%E3%82%B9%E3%83%86%E3%82%A3%E3%83%B3%E3%82%B0%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC%C3%9712EX%2BSi3%20BAIT%20CASTING%20DURA%20SENSOR%20X%2012EX%2BSI3_BAIT_CASTING_DURA_SENSOR.jpg</v>
       </c>
       <c r="I40" t="str">
         <v/>
@@ -1822,7 +1822,7 @@
         <v>Nylon</v>
       </c>
       <c r="H41" t="str">
-        <v>images/daiwa_lines/月下美人 TYPE-N 煌 GEKKABIJIN TYPE-N KIRAMEKI_Gekka_TypeN_Kou.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%20TYPE-N%20%E7%85%8C%20GEKKABIJIN%20TYPE-N%20KIRAMEKI_Gekka_TypeN_Kou.jpg</v>
       </c>
       <c r="I41" t="str">
         <v/>
@@ -1857,7 +1857,7 @@
         <v/>
       </c>
       <c r="H42" t="str">
-        <v>images/daiwa_lines/テンカラ フライライン Y TENKARA FLYLINE Y_TenkaraFryLineY.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%86%E3%83%B3%E3%82%AB%E3%83%A9%20%E3%83%95%E3%83%A9%E3%82%A4%E3%83%A9%E3%82%A4%E3%83%B3%20Y%20TENKARA%20FLYLINE%20Y_TenkaraFryLineY.jpg</v>
       </c>
       <c r="I42" t="str">
         <v/>
@@ -1892,7 +1892,7 @@
         <v>Nylon</v>
       </c>
       <c r="H43" t="str">
-        <v>images/daiwa_lines/モアザンリーダーEX II TYPE-N（ナイロン） morethan LEADER EX II TYPE-N（NYLON）_MT_LeaderType-N2_Clear.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%A2%E3%82%A2%E3%82%B6%E3%83%B3%E3%83%AA%E3%83%BC%E3%83%80%E3%83%BCEX%20II%20TYPE-N%EF%BC%88%E3%83%8A%E3%82%A4%E3%83%AD%E3%83%B3%EF%BC%89%20morethan%20LEADER%20EX%20II%20TYPE-N%EF%BC%88NYLON%EF%BC%89_MT_LeaderType-N2_Clear.jpg</v>
       </c>
       <c r="I43" t="str">
         <v/>
@@ -1927,7 +1927,7 @@
         <v/>
       </c>
       <c r="H44" t="str">
-        <v>images/daiwa_lines/月下美人 TYPE-E 白 GEKKABIJIN TYPE-E HAKU_GekkabijinTypeE_Haku_Package.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%20TYPE-E%20%E7%99%BD%20GEKKABIJIN%20TYPE-E%20HAKU_GekkabijinTypeE_Haku_Package.jpg</v>
       </c>
       <c r="I44" t="str">
         <v/>
@@ -1962,7 +1962,7 @@
         <v>Nylon</v>
       </c>
       <c r="H45" t="str">
-        <v>images/daiwa_lines/渓流ガンマ KEIRYU GAMMA_KeiryuGamma.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E6%B8%93%E6%B5%81%E3%82%AC%E3%83%B3%E3%83%9E%20KEIRYU%20GAMMA_KeiryuGamma.jpg</v>
       </c>
       <c r="I45" t="str">
         <v/>
@@ -1997,7 +1997,7 @@
         <v>Nylon</v>
       </c>
       <c r="H46" t="str">
-        <v>images/daiwa_lines/テンカラ テーパーライン TENKARA TAPER LINE_TenkaraTaperLine.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%86%E3%83%B3%E3%82%AB%E3%83%A9%20%E3%83%86%E3%83%BC%E3%83%91%E3%83%BC%E3%83%A9%E3%82%A4%E3%83%B3%20TENKARA%20TAPER%20LINE_TenkaraTaperLine.jpg</v>
       </c>
       <c r="I46" t="str">
         <v/>
@@ -2032,7 +2032,7 @@
         <v/>
       </c>
       <c r="H47" t="str">
-        <v>images/daiwa_lines/タフロン テンカラレベルライン TOUGHRON TENKARA LEVEL_ToughronTenkaraLevelLine.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%BF%E3%83%95%E3%83%AD%E3%83%B3%20%E3%83%86%E3%83%B3%E3%82%AB%E3%83%A9%E3%83%AC%E3%83%99%E3%83%AB%E3%83%A9%E3%82%A4%E3%83%B3%20TOUGHRON%20TENKARA%20LEVEL_ToughronTenkaraLevelLine.jpg</v>
       </c>
       <c r="I47" t="str">
         <v/>
@@ -2067,7 +2067,7 @@
         <v>PE</v>
       </c>
       <c r="H48" t="str">
-        <v>images/daiwa_lines/UVF 月下美人デュラヘビー×4＋1＋Si2 UVF GEKKABIJIN DURAHEAVY×4＋1＋Si2_UVF_GekkaBijinPeDuraHeavy4_1_Si2.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%E3%83%87%E3%83%A5%E3%83%A9%E3%83%98%E3%83%93%E3%83%BC%C3%974%EF%BC%8B1%EF%BC%8BSi2%20UVF%20GEKKABIJIN%20DURAHEAVY%C3%974%EF%BC%8B1%EF%BC%8BSi2_UVF_GekkaBijinPeDuraHeavy4_1_Si2.jpg</v>
       </c>
       <c r="I48" t="str">
         <v/>
@@ -2102,7 +2102,7 @@
         <v>PE</v>
       </c>
       <c r="H49" t="str">
-        <v>images/shimano_lines/Tanatoru 8_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Tanatoru%208_main.jpg</v>
       </c>
       <c r="I49" t="str">
         <v/>
@@ -2137,7 +2137,7 @@
         <v>PE</v>
       </c>
       <c r="H50" t="str">
-        <v>images/shimano_lines/Tanatoru 4 _ 8 100m  连盘_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Tanatoru%204%20_%208%20100m%20%20%E8%BF%9E%E7%9B%98_main.jpg</v>
       </c>
       <c r="I50" t="str">
         <v/>
@@ -2172,7 +2172,7 @@
         <v>PE</v>
       </c>
       <c r="H51" t="str">
-        <v>images/shimano_lines/PITBULL G9_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%20G9_main.jpg</v>
       </c>
       <c r="I51" t="str">
         <v/>
@@ -2207,7 +2207,7 @@
         <v>Nylon</v>
       </c>
       <c r="H52" t="str">
-        <v>images/shimano_lines/OCEA PLUGGER NYLON LEADER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%20PLUGGER%20NYLON%20LEADER_main.jpg</v>
       </c>
       <c r="I52" t="str">
         <v/>
@@ -2242,7 +2242,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H53" t="str">
-        <v>images/shimano_lines/PITBULL FLUORO LEADER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%20FLUORO%20LEADER_main.jpg</v>
       </c>
       <c r="I53" t="str">
         <v/>
@@ -2277,7 +2277,7 @@
         <v>PE</v>
       </c>
       <c r="H54" t="str">
-        <v>images/shimano_lines/OCEA 17+_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%2017%2B_main.jpg</v>
       </c>
       <c r="I54" t="str">
         <v/>
@@ -2312,7 +2312,7 @@
         <v>PE</v>
       </c>
       <c r="H55" t="str">
-        <v>images/shimano_lines/OCEA 8_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%208_main.jpg</v>
       </c>
       <c r="I55" t="str">
         <v/>
@@ -2347,7 +2347,7 @@
         <v>PE</v>
       </c>
       <c r="H56" t="str">
-        <v>images/shimano_lines/OCEA JIGGER MX4_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%20JIGGER%20MX4_main.jpg</v>
       </c>
       <c r="I56" t="str">
         <v/>
@@ -2382,7 +2382,7 @@
         <v>PE</v>
       </c>
       <c r="H57" t="str">
-        <v>images/shimano_lines/KISU SPECIAL EX4_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/KISU%20SPECIAL%20EX4%2013m_main.jpg</v>
       </c>
       <c r="I57" t="str">
         <v/>
@@ -2417,7 +2417,7 @@
         <v>PE</v>
       </c>
       <c r="H58" t="str">
-        <v>images/shimano_lines/KISU SPECIAL G5_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/KISU%20SPECIAL%20G5_main.jpg</v>
       </c>
       <c r="I58" t="str">
         <v/>
@@ -2452,7 +2452,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H59" t="str">
-        <v>images/shimano_lines/OCEA EX 前导线_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%20EX%20%E5%89%8D%E5%AF%BC%E7%BA%BF_main.jpg</v>
       </c>
       <c r="I59" t="str">
         <v/>
@@ -2487,7 +2487,7 @@
         <v>PE</v>
       </c>
       <c r="H60" t="str">
-        <v>images/shimano_lines/LIMITED PRO G5+ PE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/LIMITED%20PRO%20G5%2B%20PE_main.jpg</v>
       </c>
       <c r="I60" t="str">
         <v/>
@@ -2522,7 +2522,7 @@
         <v>PE</v>
       </c>
       <c r="H61" t="str">
-        <v>images/shimano_lines/PITBULL 12_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%2012_main.jpg</v>
       </c>
       <c r="I61" t="str">
         <v/>
@@ -2557,7 +2557,7 @@
         <v>PE</v>
       </c>
       <c r="H62" t="str">
-        <v>images/shimano_lines/HARDBULL 8+_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/HARDBULL%208%2B_main.jpg</v>
       </c>
       <c r="I62" t="str">
         <v/>
@@ -2592,7 +2592,7 @@
         <v>PE</v>
       </c>
       <c r="H63" t="str">
-        <v>images/shimano_lines/GRAPPLER 8_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/GRAPPLER%208_main.jpg</v>
       </c>
       <c r="I63" t="str">
         <v/>
@@ -2627,7 +2627,7 @@
         <v>PE</v>
       </c>
       <c r="H64" t="str">
-        <v>images/shimano_lines/KISU SPECIAL EX4 13m_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/KISU%20SPECIAL%20EX4%2013m_main.jpg</v>
       </c>
       <c r="I64" t="str">
         <v/>
@@ -2662,7 +2662,7 @@
         <v>PE</v>
       </c>
       <c r="H65" t="str">
-        <v>images/shimano_lines/Tanatoru 4_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Tanatoru%204%20_%208%20100m%20%20%E8%BF%9E%E7%9B%98_main.jpg</v>
       </c>
       <c r="I65" t="str">
         <v/>
@@ -2697,7 +2697,7 @@
         <v>Nylon</v>
       </c>
       <c r="H66" t="str">
-        <v>images/shimano_lines/KAIKON_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/KAIKON_main.jpg</v>
       </c>
       <c r="I66" t="str">
         <v/>
@@ -2732,7 +2732,7 @@
         <v>Nylon</v>
       </c>
       <c r="H67" t="str">
-        <v>images/shimano_lines/BULL'S EYE 远投_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BULL'S%20EYE%20%E8%BF%9C%E6%8A%95_main.jpg</v>
       </c>
       <c r="I67" t="str">
         <v/>
@@ -2767,7 +2767,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H68" t="str">
-        <v>images/shimano_lines/OCEA JIGGER MASTER 前导线_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%20JIGGER%20MASTER%20%E5%89%8D%E5%AF%BC%E7%BA%BF_main.jpg</v>
       </c>
       <c r="I68" t="str">
         <v/>
@@ -2802,7 +2802,7 @@
         <v>PE</v>
       </c>
       <c r="H69" t="str">
-        <v>images/shimano_lines/Sephia 8+_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Sephia%208%2B_main.jpg</v>
       </c>
       <c r="I69" t="str">
         <v/>
@@ -2837,7 +2837,7 @@
         <v>PE</v>
       </c>
       <c r="H70" t="str">
-        <v>images/shimano_lines/PITBULL 8+_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%208%2B_main.jpg</v>
       </c>
       <c r="I70" t="str">
         <v/>
@@ -2872,7 +2872,7 @@
         <v>Ester</v>
       </c>
       <c r="H71" t="str">
-        <v>images/shimano_lines/FUKASE 船_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/FUKASE%20%E8%88%B9_main.jpg</v>
       </c>
       <c r="I71" t="str">
         <v/>
@@ -2907,7 +2907,7 @@
         <v>PE</v>
       </c>
       <c r="H72" t="str">
-        <v>images/shimano_lines/Sephia G5_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Sephia%20G5_main.jpg</v>
       </c>
       <c r="I72" t="str">
         <v/>
@@ -2942,7 +2942,7 @@
         <v>PE</v>
       </c>
       <c r="H73" t="str">
-        <v>images/shimano_lines/Sephia 8_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Sephia%208%2B_main.jpg</v>
       </c>
       <c r="I73" t="str">
         <v/>
@@ -2977,7 +2977,7 @@
         <v>PE</v>
       </c>
       <c r="H74" t="str">
-        <v>images/shimano_lines/SPINPOWER EX4_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/SPINPOWER%20EX4_main.jpg</v>
       </c>
       <c r="I74" t="str">
         <v/>
@@ -3012,7 +3012,7 @@
         <v>PE</v>
       </c>
       <c r="H75" t="str">
-        <v>images/shimano_lines/GRAPPLER 4_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/GRAPPLER%204_main.jpg</v>
       </c>
       <c r="I75" t="str">
         <v/>
@@ -3047,7 +3047,7 @@
         <v>PE</v>
       </c>
       <c r="H76" t="str">
-        <v>images/shimano_lines/LAKEMASTER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/LAKEMASTER_main.jpg</v>
       </c>
       <c r="I76" t="str">
         <v/>
@@ -3082,7 +3082,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H77" t="str">
-        <v>images/shimano_lines/LIMITED PRO MASTER TOUGH-MUD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/LIMITED%20PRO%20MASTER%20TOUGH-MUD_main.jpg</v>
       </c>
       <c r="I77" t="str">
         <v/>
@@ -3117,7 +3117,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H78" t="str">
-        <v>images/shimano_lines/LIMITED PRO MASTER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/LIMITED%20PRO%20MASTER%20TOUGH-MUD_main.jpg</v>
       </c>
       <c r="I78" t="str">
         <v/>
@@ -3152,7 +3152,7 @@
         <v>Nylon</v>
       </c>
       <c r="H79" t="str">
-        <v>images/shimano_lines/BB-X HYPER-REPEL α 漂浮_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BB-X%20HYPER-REPEL%20%CE%B1%20%E6%BC%82%E6%B5%AE_main.jpg</v>
       </c>
       <c r="I79" t="str">
         <v/>
@@ -3187,7 +3187,7 @@
         <v>Nylon</v>
       </c>
       <c r="H80" t="str">
-        <v>images/shimano_lines/BB-X PLASMA WHITE FLOAT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BB-X%20PLASMA%20WHITE%20FLOAT_main.jpg</v>
       </c>
       <c r="I80" t="str">
         <v/>
@@ -3222,7 +3222,7 @@
         <v>PE</v>
       </c>
       <c r="H81" t="str">
-        <v>images/shimano_lines/PITBULL 4_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%204%2B_main.jpg</v>
       </c>
       <c r="I81" t="str">
         <v/>
@@ -3257,7 +3257,7 @@
         <v>Nylon</v>
       </c>
       <c r="H82" t="str">
-        <v>images/shimano_lines/LIMITED PRO HYPER-REPEL α ZERO 漂浮_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/LIMITED%20PRO%20HYPER-REPEL%20%CE%B1%20ZERO%20%E6%BC%82%E6%B5%AE_main.jpg</v>
       </c>
       <c r="I82" t="str">
         <v/>
@@ -3292,7 +3292,7 @@
         <v>Nylon</v>
       </c>
       <c r="H83" t="str">
-        <v>images/shimano_lines/LIMITED PRO 矶 ZERO 悬停 150m_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/LIMITED%20PRO%20%E7%9F%B6%20ZERO%20%E6%82%AC%E5%81%9C%20150m_main.jpg</v>
       </c>
       <c r="I83" t="str">
         <v/>
@@ -3327,7 +3327,7 @@
         <v>Nylon</v>
       </c>
       <c r="H84" t="str">
-        <v>images/shimano_lines/BB-X PLASMA WHITE ZERO SUSPEND_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BB-X%20PLASMA%20WHITE%20ZERO%20SUSPEND_main.jpg</v>
       </c>
       <c r="I84" t="str">
         <v/>
@@ -3362,7 +3362,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H85" t="str">
-        <v>images/shimano_lines/MASTIFF FC 90m_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/MASTIFF%20FC%2090m_main.jpg</v>
       </c>
       <c r="I85" t="str">
         <v/>
@@ -3397,7 +3397,7 @@
         <v>Nylon</v>
       </c>
       <c r="H86" t="str">
-        <v>images/shimano_lines/OCEA 前导线_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%20%E5%89%8D%E5%AF%BC%E7%BA%BF_main.jpg</v>
       </c>
       <c r="I86" t="str">
         <v/>
@@ -3432,7 +3432,7 @@
         <v>Nylon</v>
       </c>
       <c r="H87" t="str">
-        <v>images/shimano_lines/FIREBLOOD HYPER-REPEL α ZERO 漂浮_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/FIREBLOOD%20HYPER-REPEL%20%CE%B1%20ZERO%20%E6%BC%82%E6%B5%AE_main.jpg</v>
       </c>
       <c r="I87" t="str">
         <v/>
@@ -3467,7 +3467,7 @@
         <v>Nylon</v>
       </c>
       <c r="H88" t="str">
-        <v>images/shimano_lines/FIREBLOOD HYPER-REPEL α ZERO 悬停_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/FIREBLOOD%20HYPER-REPEL%20%CE%B1%20ZERO%20%E6%82%AC%E5%81%9C_main.jpg</v>
       </c>
       <c r="I88" t="str">
         <v/>
@@ -3502,7 +3502,7 @@
         <v>Nylon</v>
       </c>
       <c r="H89" t="str">
-        <v>images/shimano_lines/BB-X HYPER-REPEL α 悬停_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BB-X%20HYPER-REPEL%20%CE%B1%20%E6%82%AC%E5%81%9C_main.jpg</v>
       </c>
       <c r="I89" t="str">
         <v/>
@@ -3537,7 +3537,7 @@
         <v>PE</v>
       </c>
       <c r="H90" t="str">
-        <v>images/shimano_lines/OCEA 16 30m_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%2016%2030m_main.jpg</v>
       </c>
       <c r="I90" t="str">
         <v/>
@@ -3572,7 +3572,7 @@
         <v>PE</v>
       </c>
       <c r="H91" t="str">
-        <v>images/shimano_lines/PITBULL 4+_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%204%2B_main.jpg</v>
       </c>
       <c r="I91" t="str">
         <v/>
@@ -3607,7 +3607,7 @@
         <v>PE</v>
       </c>
       <c r="H92" t="str">
-        <v>images/shimano_lines/BASIS G5 PE SUSPEND_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BASIS%20G5%20PE%20SUSPEND_main.jpg</v>
       </c>
       <c r="I92" t="str">
         <v/>
@@ -3642,7 +3642,7 @@
         <v>Nylon</v>
       </c>
       <c r="H93" t="str">
-        <v>images/shimano_lines/FIREBLOOD STRETCH 悬停_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/FIREBLOOD%20STRETCH%20%E6%82%AC%E5%81%9C_main.jpg</v>
       </c>
       <c r="I93" t="str">
         <v/>
@@ -3677,7 +3677,7 @@
         <v>Ester</v>
       </c>
       <c r="H94" t="str">
-        <v>images/shimano_lines/SIGHT LASER EX 240m_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/SIGHT%20LASER%20EX%20240m_main.jpg</v>
       </c>
       <c r="I94" t="str">
         <v/>
@@ -3712,7 +3712,7 @@
         <v>PE</v>
       </c>
       <c r="H95" t="str">
-        <v>images/shimano_lines/PITBULL G5_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%20G5_main.jpg</v>
       </c>
       <c r="I95" t="str">
         <v/>
@@ -3747,7 +3747,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H96" t="str">
-        <v>images/shimano_lines/Soare AJING 150m_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Soare%20AJING%20150m_main.jpg</v>
       </c>
       <c r="I96" t="str">
         <v/>
@@ -3782,7 +3782,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H97" t="str">
-        <v>images/shimano_lines/Sephia MASTER 前导线 30m_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Sephia%20MASTER%20%E5%89%8D%E5%AF%BC%E7%BA%BF%2030m_main.jpg</v>
       </c>
       <c r="I97" t="str">
         <v/>
@@ -3817,7 +3817,7 @@
         <v>PE</v>
       </c>
       <c r="H98" t="str">
-        <v>images/shimano_lines/BB BRAID_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BB%20BRAID_main.jpg</v>
       </c>
       <c r="I98" t="str">
         <v/>
@@ -3852,7 +3852,7 @@
         <v>Nylon</v>
       </c>
       <c r="H99" t="str">
-        <v>images/shimano_lines/BAISIS 矶_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BAISIS%20%E7%9F%B6_main.jpg</v>
       </c>
       <c r="I99" t="str">
         <v/>
@@ -3887,7 +3887,7 @@
         <v>Nylon</v>
       </c>
       <c r="H100" t="str">
-        <v>images/shimano_lines/BASIS ORANGE ZERO SUSPEND_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BASIS%20ORANGE%20ZERO%20SUSPEND_main.jpg</v>
       </c>
       <c r="I100" t="str">
         <v/>
@@ -3922,7 +3922,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H101" t="str">
-        <v>images/shimano_lines/BAISIS EX_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BAISIS%20EX_main.jpg</v>
       </c>
       <c r="I101" t="str">
         <v/>
@@ -3957,7 +3957,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H102" t="str">
-        <v>images/shimano_lines/EXSENCE 前导线 EX 30m_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/EXSENCE%20%E5%89%8D%E5%AF%BC%E7%BA%BF%20EX%2030m_main.jpg</v>
       </c>
       <c r="I102" t="str">
         <v/>
@@ -3992,7 +3992,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H103" t="str">
-        <v>images/shimano_lines/炎月 EX 前导线 30m_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/%E7%82%8E%E6%9C%88%20EX%20%E5%89%8D%E5%AF%BC%E7%BA%BF%2030m_main.jpg</v>
       </c>
       <c r="I103" t="str">
         <v/>
@@ -4027,7 +4027,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H104" t="str">
-        <v>images/shimano_lines/Soare 前导线 EX 30m_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Soare%20%E5%89%8D%E5%AF%BC%E7%BA%BF%20EX%2030m_main.jpg</v>
       </c>
       <c r="I104" t="str">
         <v/>
@@ -4062,7 +4062,7 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H105" t="str">
-        <v>images/shimano_lines/Sephia 前导线 30m_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Sephia%20%E5%89%8D%E5%AF%BC%E7%BA%BF%2030m_main.jpg</v>
       </c>
       <c r="I105" t="str">
         <v/>
@@ -4097,7 +4097,7 @@
         <v>Nylon</v>
       </c>
       <c r="H106" t="str">
-        <v>images/shimano_lines/LIMITED PRO 前导线 悬停_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/LIMITED%20PRO%20%E5%89%8D%E5%AF%BC%E7%BA%BF%20%E6%82%AC%E5%81%9C_main.jpg</v>
       </c>
       <c r="I106" t="str">
         <v/>
@@ -4132,7 +4132,7 @@
         <v>PE</v>
       </c>
       <c r="H107" t="str">
-        <v>images/shimano_lines/PITBULL 8_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%208%2B_main.jpg</v>
       </c>
       <c r="I107" t="str">
         <v/>

--- a/GearSage-client/rate/excel/line.xlsx
+++ b/GearSage-client/rate/excel/line.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K107"/>
+  <dimension ref="A1:K92"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -442,10 +442,10 @@
         <v>2</v>
       </c>
       <c r="C2" t="str">
-        <v>フィネス ブレイブ Z FINESSE BRAVE Z</v>
+        <v>BAIT CASTING DURA SENSOR X 12EX+SI3</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>BAIT CASTING DURA SENSOR X 12EX+SI3</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -454,19 +454,19 @@
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>Fluorocarbon</v>
+        <v>PE</v>
       </c>
       <c r="H2" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%95%E3%82%A3%E3%83%8D%E3%82%B9%20%E3%83%96%E3%83%AC%E3%82%A4%E3%83%96%20Z%20FINESSE%20BRAVE%20Z_FinesseBraveZ_4lb.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/BAIT%20CASTING%20DURA%20SENSOR%20X%2012EX%2BSI3_main.jpg</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="J2" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="K2" t="str">
-        <v>極細フィネス設計のダイワ最高峰フロロライン</v>
+        <v>專為拋投設計的專用PE線!減少線材糾結問題,提升拋投距離! / 強韌PE 在DURA SENSOR系列中,特別緊密編織成的PE線。由UVF / TOUGH PE / Evo Silicone2、Evo Silicone3 / MUSCLE BRAIDING 四項技術構成的高密度PE線。特點是耐磨、提升耐用性、降低噪音、增加拋投距離且減少不必要的麻煩。</v>
       </c>
     </row>
     <row r="3">
@@ -477,10 +477,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="str">
-        <v>BASS-Xフロロ 240 BASS-X FLUORO 240</v>
+        <v>METACOMPO DURA HEAVY</v>
       </c>
       <c r="D3" t="str">
-        <v/>
+        <v>METACOMPO DURA HEAVY</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -489,19 +489,19 @@
         <v/>
       </c>
       <c r="G3" t="str">
-        <v>Fluorocarbon</v>
+        <v>Composite</v>
       </c>
       <c r="H3" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/BASS-X%E3%83%95%E3%83%AD%E3%83%AD%20240%20BASS-X%20FLUORO%20240_BASS-X-FLUORO-240_8.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/METACOMPO%20DURA%20HEAVY_main.jpg</v>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="J3" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="K3" t="str">
-        <v>BASS-X　フロロ,BASS-X,フロロ,フロロ 240,ライン,バス フロロ,バスXフロロ,BASS-X フロロ240</v>
+        <v>耐磨性大幅提升的「高比重5.0複合金屬線」 / 耐磨性大幅提升的「高比重5.0 複合金屬線」</v>
       </c>
     </row>
     <row r="4">
@@ -512,10 +512,10 @@
         <v>2</v>
       </c>
       <c r="C4" t="str">
-        <v>UVF タトゥーラ センサー×8＋Si2 UVF TATULA SENSOR×8+Si2</v>
+        <v>UVF EMERALDAS DURA SENSOR X 12EX+SI3</v>
       </c>
       <c r="D4" t="str">
-        <v/>
+        <v>UVF EMERALDAS DURA SENSOR X 12EX+SI3</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -527,16 +527,16 @@
         <v>PE</v>
       </c>
       <c r="H4" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E3%82%BF%E3%83%88%E3%82%A5%E3%83%BC%E3%83%A9%20%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC%C3%978%EF%BC%8BSi2%20UVF%20TATULA%20SENSOR%C3%978%2BSi2_UVFTatulaSensor8-Si2.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20EMERALDAS%20DURA%20SENSOR%20X%2012EX%2BSI3_main.jpg</v>
       </c>
       <c r="I4" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="J4" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="K4" t="str">
-        <v>強力、感度、耐摩耗性にすぐれたパワーフィネスにベストマッチな8ブレイドPEライン。</v>
+        <v>強韌的關鍵在於編織技法。Muscle 12Braid引領的『新』世界! / DaiwaPE線中最具「柔韌性」。專為木蝦釣法設計的特殊釣線。 / 為了讓與烏賊關聯的所有時間,都充滿感動。「EMERALDAS」。這是DAIWA率先於全球推出的烏賊遊戲專用綜合釣具品牌。為將烏賊帶入您手中。更為在迎接巔峰時刻前,與烏賊關聯的每分每秒,皆能充滿感動而存在。爽快的鉤組手感。從下落、停留到刺魚,在原本只需靜候的時光裡,持續傳遞變化與徵兆的靈敏度。即使與大魚搏鬥也能安心的可靠感。更因整體設計方能實現的快適操作感,以及在相機捲中格外出眾的攝影美感。EMERALDAS。自從握在手中的那一刻起,願隨時隨地,永遠獻上感動。</v>
       </c>
     </row>
     <row r="5">
@@ -547,10 +547,10 @@
         <v>2</v>
       </c>
       <c r="C5" t="str">
-        <v>スティーズ フロロ X’LINK STEEZ FLUORO X’LINK</v>
+        <v>STEEZ氟碳線 堅韌</v>
       </c>
       <c r="D5" t="str">
-        <v/>
+        <v>STEEZ氟碳線 堅韌</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -562,16 +562,16 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H5" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%95%E3%83%AD%E3%83%AD%20X%E2%80%99LINK%20STEEZ%20FLUORO%20X%E2%80%99LINK_SteezFluoroXLink.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/STEEZ%E6%B0%9F%E7%A2%B3%E7%B7%9A%20%E5%A0%85%E9%9F%8C_main.png</v>
       </c>
       <c r="I5" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="J5" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="K5" t="str">
-        <v>ダイワの最新テクノロジーで新たに誕生した「頂上フロロ」。これが最強。まさに「頂上」。</v>
+        <v>追求高耐久性的「堅韌」規格特別系列。 / 獻給那些真心投入鱸魚釣魚的人們。打造能與真心對待鱸魚、將鱸魚釣法視為生活核心的釣客產生共鳴的產品。這正是開發團隊傾注心血的結晶--旨在透過產品與訊息傳遞DAIWA對鱸魚釣法的熱忱,打造出能與釣客心靈相通的品牌。為此,我們以DAIWA的技術與信念,嚴謹不懈地精雕細琢。不僅是釣竿,不僅是捲線器,更蘊含著對所有迎戰鱸魚裝備的熱忱。與真心熱愛鱸魚釣的釣友們共同燃燒的熱情⋯⋯這便是「STEEZ」。</v>
       </c>
     </row>
     <row r="6">
@@ -582,10 +582,10 @@
         <v>2</v>
       </c>
       <c r="C6" t="str">
-        <v>モンスター ブレイブ Z MONSTER BRAVE Z</v>
+        <v>UVF PE DURAHEAVY×8+1+Si2</v>
       </c>
       <c r="D6" t="str">
-        <v/>
+        <v>UVF PE DURAHEAVY×8+1+Si2</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -594,19 +594,19 @@
         <v/>
       </c>
       <c r="G6" t="str">
-        <v>Fluorocarbon</v>
+        <v>PE</v>
       </c>
       <c r="H6" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%A2%E3%83%B3%E3%82%B9%E3%82%BF%E3%83%BC%20%E3%83%96%E3%83%AC%E3%82%A4%E3%83%96%20Z%20MONSTER%20BRAVE%20Z_MonsterBraveZ_18lb.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20PE%20DURAHEAVY%C3%978%2B1%2BSi2_main.jpg</v>
       </c>
       <c r="I6" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="J6" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="K6" t="str">
-        <v>モンスターバスをターゲットとした高品質フロロライン</v>
+        <v>具備優異耐磨性與耐久性的高密度「Muscle PE」推出高比重類型 / 具備優異耐磨性與耐久性的高密度「肌肉型PE」推出高比重類型 / 高比重PE(芯線採用高比重FEP)。PE8根+FEP1根的「8+1結構」。沉降的PE會改變攻擊方式。肌肉PE(高密度PE)。因採用高密度編織工藝(相較本公司其他產品),釣線品質大幅提升。「抗摩擦性強化/耐久性提升/減震降噪/飛距增加」。・「TOUGH PE」×「NEW Evo Silicone2」=耐磨性提升300%以上(相較於本公司產品)・TOUGH PE⇒原釣線變太且呈真圓形,提升強度。・New Evo Silicone2加工⇒提升耐久性/表面更光滑,有效降低異音產生。・UVF加工(超高密度纖維加工)⇒強度提升、靈敏度提升(相較於本公司同類產品)・肌肉編織⇒透過密集編織提升抗衝擊斷裂能力。</v>
       </c>
     </row>
     <row r="7">
@@ -617,10 +617,10 @@
         <v>2</v>
       </c>
       <c r="C7" t="str">
-        <v>スティーズ デュラブラ マックス STEEZ DURABRA MAX</v>
+        <v>UVF SALTIGA DURA SENSOR×8+Si2</v>
       </c>
       <c r="D7" t="str">
-        <v/>
+        <v>UVF SALTIGA DURA SENSOR×8+Si2</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -629,19 +629,19 @@
         <v/>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>PE</v>
       </c>
       <c r="H7" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%20%E3%83%87%E3%83%A5%E3%83%A9%E3%83%96%E3%83%A9%20%E3%83%9E%E3%83%83%E3%82%AF%E3%82%B9%20STEEZ%20DURABRA%20MAX_SteezDurabraMax.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20SALTIGA%20DURA%20SENSOR%C3%978%2BSi2_main.jpg</v>
       </c>
       <c r="I7" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="J7" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="K7" t="str">
-        <v>コスレに強い、耐摩耗MAX。</v>
+        <v>壓倒性耐磨性「DuraSensor」。 / 壓倒的耐磨性「DuraSensor」。 / 打破你的紀錄 -抓住夢想-「總有一天,要釣到那條魚。」為實現釣友夢想而誕生的「SALTIGA」。承襲DAIWA離岸釣最強基因,持續以最新科技進化。前提是與未知大魚對峙。持續挑戰釣具的極限,追求各部位的強度與易用性,追求能帶來優性能的性能。SALTIGA肩負的使命,正是成為能確實引領釣友接近夢幻魚種的釣具。持續實現其存在意義,即意味著釣友的夢想得以實現。這份值得信賴的性能,正支持著全球釣友的夢想。</v>
       </c>
     </row>
     <row r="8">
@@ -652,10 +652,10 @@
         <v>2</v>
       </c>
       <c r="C8" t="str">
-        <v>バス-X フロロ BASS-X FLUORO</v>
+        <v>ASTRON 石鯛 MAX GAMMA</v>
       </c>
       <c r="D8" t="str">
-        <v/>
+        <v>ASTRON 石鯛 MAX GAMMA</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -664,19 +664,19 @@
         <v/>
       </c>
       <c r="G8" t="str">
-        <v>Fluorocarbon</v>
+        <v>Nylon</v>
       </c>
       <c r="H8" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%90%E3%82%B9-X%20%E3%83%95%E3%83%AD%E3%83%AD%20BASS-X%20FLUORO_BASS-X100m_1.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/ASTRON%20%E7%9F%B3%E9%AF%9B%20MAX%20GAMMA_main.jpg</v>
       </c>
       <c r="I8" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="J8" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="K8" t="str">
-        <v>高級しなやかフロロが300ｍバルクで平行巻。</v>
+        <v>耐磨性提升2000%[20倍(本公司比)]的柔韌尼龍石鯛母線近投類型。 / 耐磨耗性能提升 2000%[20倍(與本公司比)]!具備極佳柔韌性的石鯛專用近投型尼龍母線。 / 透過特殊技術(NANODIS MAX),將耐磨劑微分散於尼龍分子中,使耐磨性提升至2,000%(20倍)。在頻繁發生根部磨損的狀況下發揮效果。透過強化結節結構,實現更高一級的強度。採用易於操控的柔韌設計,有效消除太柄常見的捲線困擾。適度抑制延展性,提升觸感靈敏度,同時更易傳遞刺魚力道。配色採用以迷彩為概念的黑色海洋。捲繞捲線器時,附有方便的50公尺標記貼紙。平行卷DPLS尼龍 比重1.14</v>
       </c>
     </row>
     <row r="9">
@@ -687,10 +687,10 @@
         <v>2</v>
       </c>
       <c r="C9" t="str">
-        <v>UVF フロッグデュラセンサー×8＋Si2 UVF FROG DURA SENSOR×8+Si2</v>
+        <v>UVF PE DURASENSOR X8EX+SI3</v>
       </c>
       <c r="D9" t="str">
-        <v/>
+        <v>UVF PE DURASENSOR X8EX+SI3</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -702,16 +702,16 @@
         <v>PE</v>
       </c>
       <c r="H9" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E3%83%95%E3%83%AD%E3%83%83%E3%82%B0%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC%C3%978%EF%BC%8BSi2%20UVF%20FROG%20DURA%20SENSOR%C3%978%2BSi2_UVFFrogDuraSensor8PlusSi2.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20PE%20DURASENSOR%20X8EX%2BSI3_main.jpg</v>
       </c>
       <c r="I9" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="J9" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="K9" t="str">
-        <v>内山幸也氏監修：こだわりの「フロッグ専用PE」＝８ブレイド+TOUGH PE×NEW Evo Silicone&lt;sup&gt;2&lt;/sup&gt;で高強力、高感度、 耐摩耗性300％以上(当社比)</v>
+        <v>釣線體表面極致光滑!高規格八股線! / 釣線表面極致平滑!高規格8束編織PE 線。 / 採用大和獨家「EX加工」技術,使釣線體表面極致光滑,不僅提升拋投距離,更有效減少釣線異音與雜質附著。採用強化版+Si3加工技術取代+Si2,不僅提升抗磨損性能,更進一步強化了耐久性。此外,由於編織密度較高(相較於本公司其他產品),作為釣線的品質獲得顯著提升。</v>
       </c>
     </row>
     <row r="10">
@@ -722,10 +722,10 @@
         <v>2</v>
       </c>
       <c r="C10" t="str">
-        <v>バス-X ナイロン BASS-X NYLON</v>
+        <v>UVF サーフデュラ感測器×8+Si2</v>
       </c>
       <c r="D10" t="str">
-        <v/>
+        <v>UVF サーフデュラ感測器×8+Si2</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -734,19 +734,19 @@
         <v/>
       </c>
       <c r="G10" t="str">
-        <v>Nylon</v>
+        <v>PE</v>
       </c>
       <c r="H10" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%90%E3%82%B9-X%20%E3%83%8A%E3%82%A4%E3%83%AD%E3%83%B3%20BASS-X%20NYLON_BassXNylon.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E3%82%B5%E3%83%BC%E3%83%95%E3%83%87%E3%83%A5%E3%83%A9%E6%84%9F%E6%B8%AC%E5%99%A8%C3%978%2BSi2_main.jpg</v>
       </c>
       <c r="I10" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="J10" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="K10" t="str">
-        <v>極上高級ラインが300ｍバルクで平行巻。</v>
+        <v>具備優異耐磨性與耐久性的高密度「肌肉PE」! / 因採用高密度編織工藝(相較本公司其他產品),釣線品質大幅提升。「抗摩擦性強化/耐久性提升/減震降噪/飛距增加」。TOUGH PE×NEW EvoSilicone2=耐磨性提升300%以上(相較於本公司產品)。採用密實編織的肌理編織加工,具備優異抗衝擊斷裂特性。各色中心12.5m處附黑色標記。</v>
       </c>
     </row>
     <row r="11">
@@ -757,10 +757,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="str">
-        <v>スティーズフロロ タフネス STEEZ FLUORO TOUGHNESS</v>
+        <v>UVF EMERALDAS DURAHEAVY×8+1+Si3</v>
       </c>
       <c r="D11" t="str">
-        <v/>
+        <v>UVF EMERALDAS DURAHEAVY×8+1+Si3</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -769,19 +769,19 @@
         <v/>
       </c>
       <c r="G11" t="str">
-        <v>Fluorocarbon</v>
+        <v>PE</v>
       </c>
       <c r="H11" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%B9%E3%83%86%E3%82%A3%E3%83%BC%E3%82%BA%E3%83%95%E3%83%AD%E3%83%AD%20%E3%82%BF%E3%83%95%E3%83%8D%E3%82%B9%20STEEZ%20FLUORO%20TOUGHNESS_STEEZ-FLUORO-TOUGHNESS.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20EMERALDAS%20DURAHEAVY%C3%978%2B1%2BSi3_main.jpg</v>
       </c>
       <c r="I11" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="J11" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="K11" t="str">
-        <v>高い耐久性を追求した「タフネス」仕様のスペシャルライン。</v>
+        <v>快速適應海水環境、不易受風力影響的「沉水型」PE釣線「SS」全面進化! / 為了讓與烏賊關聯的所有時間,都充滿感動。「EMERALDAS」。這是DAIWA率先於全球推出的烏賊遊戲專用綜合釣具品牌。為將烏賊帶入您手中。更為在迎接巔峰時刻前,與烏賊關聯的每分每秒,皆能充滿感動而存在。爽快的鉤組手感。從下落、停留到刺魚,在原本只需靜候的時光裡,持續傳遞變化與徵兆的靈敏度。即使與大魚搏鬥也能安心的可靠感。更因整體設計方能實現的快適操作感,以及在相機捲中格外出眾的攝影美感。EMERALDAS。自從握在手中的那一刻起,願隨時隨地,永遠獻上感動。</v>
       </c>
     </row>
     <row r="12">
@@ -792,10 +792,10 @@
         <v>2</v>
       </c>
       <c r="C12" t="str">
-        <v>タトゥーラ タイプ ナイロン TATULA Type NYLON</v>
+        <v>磯DURASENSOR×8SS+Si2</v>
       </c>
       <c r="D12" t="str">
-        <v/>
+        <v>磯DURASENSOR×8SS+Si2</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -804,19 +804,19 @@
         <v/>
       </c>
       <c r="G12" t="str">
-        <v>Nylon</v>
+        <v>PE</v>
       </c>
       <c r="H12" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%BF%E3%83%88%E3%82%A5%E3%83%BC%E3%83%A9%20%E3%82%BF%E3%82%A4%E3%83%97%20%E3%83%8A%E3%82%A4%E3%83%AD%E3%83%B3%20TATULA%20Type%20NYLON_TatulaTypeNylon.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E7%A3%AFDURASENSOR%C3%978SS%2BSi2_main.jpg</v>
       </c>
       <c r="I12" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="J12" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="K12" t="str">
-        <v>こだわりの低伸度設計と高強力・ 高耐摩耗性をバランスよく両立、 UWR加工で軽量ルアーをストレ スなく飛ばせる</v>
+        <v>岩岸用PE線TOUGH PE×Si2 8股編織線登場!真圓性提升,卓越張力持久不衰!導環纏繞更大幅減少! / 磯釣專用 PE 線搭載 TOUGH PE × Si2 8束編織技術正式登場!真圓度再進化,釣線的張力極佳更堅硬!大幅減少導環纏線問題! / TOUGH PE×Si2=耐磨性提升300%以上(相較於本公司產品)。PE×4、酯類×4的混合類型8股編織線。採用與尼龍等講究的比重1.1材質,因此能如尼龍般使用.採用八股線設計提升真圓度,因酯類含量高,張力持久耐用,即使長期使用仍能大幅減少導環纏繞現象。輕量仕掛搭配尼龍母線時,能展現超越其極限的飛距,因此以往只能放棄的遠場釣點,如今也能直接攻克。因徑徑細小,即使將仕掛投入水中,母線也不易受近岸水流影響,能與誘餌長時間保持同步。因觸感靈敏度提升,可減少因提竿時機延遲導致尾長魚吞鉤,進而造成魚線被咬斷的情況。混合聚乙烯 比重 1.1</v>
       </c>
     </row>
     <row r="13">
@@ -827,10 +827,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="str">
-        <v>プレッソエリアエステル TT PRESSO AREA ESTER TECHNICAL TUNE</v>
+        <v>SALTIGA FLUORO LEADER X’LINK</v>
       </c>
       <c r="D13" t="str">
-        <v/>
+        <v>SALTIGA FLUORO LEADER X’LINK</v>
       </c>
       <c r="E13" t="str">
         <v/>
@@ -839,19 +839,19 @@
         <v/>
       </c>
       <c r="G13" t="str">
-        <v>Ester</v>
+        <v>Fluorocarbon</v>
       </c>
       <c r="H13" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%E3%82%A8%E3%83%AA%E3%82%A2%E3%82%A8%E3%82%B9%E3%83%86%E3%83%AB%20TT%20PRESSO%20AREA%20ESTER%20TECHNICAL%20TUNE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/SALTIGA%20FLUORO%20LEADER%20X%E2%80%99LINK_main.jpg</v>
       </c>
       <c r="I13" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="J13" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="K13" t="str">
-        <v>和田テスターこだわりの競技モデル！1匹でも多くキャッチするためのテクニカルチューン（TT)！</v>
+        <v>DAIWA最新科技所誕生的「頂上氟碳線」。此乃最強。正是「頂上」。 / 結合 DAIWA 最新頂尖科技、全新誕生的「頂尖碳纖線」。這就是最強,無愧於「頂尖」之名 / 打破你的紀錄 -抓住夢想-「總有一天,要釣到那條魚。」為實現釣友夢想而誕生的「SALTIGA」。承襲DAIWA離岸釣最強基因,持續以最新科技進化。前提是與未知大魚對峙。持續挑戰釣具的極限,追求各部位的強度與易用性,追求能帶來優性能的性能。SALTIGA肩負的使命,正是成為能確實引領釣友接近夢幻魚種的釣具。持續實現其存在意義,即意味著釣友的夢想得以實現。這份值得信賴的性能,正支持著全球釣友的夢想。</v>
       </c>
     </row>
     <row r="14">
@@ -862,10 +862,10 @@
         <v>2</v>
       </c>
       <c r="C14" t="str">
-        <v>トラウトフロロリーダー TROUT FLUORO LEADER</v>
+        <v>UVF EMERALDAS DURASENSOR X8EX+SI3 IM</v>
       </c>
       <c r="D14" t="str">
-        <v/>
+        <v>UVF EMERALDAS DURASENSOR X8EX+SI3 IM</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -874,19 +874,19 @@
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>Fluorocarbon</v>
+        <v>PE</v>
       </c>
       <c r="H14" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%88%E3%83%A9%E3%82%A6%E3%83%88%E3%83%95%E3%83%AD%E3%83%AD%E3%83%AA%E3%83%BC%E3%83%80%E3%83%BC%20TROUT%20FLUORO%20LEADER_TroutFluoroLeader_3lb.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20EMERALDAS%20DURASENSOR%20X8EX%2BSI3%20IM_main.jpg</v>
       </c>
       <c r="I14" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="J14" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="K14" t="str">
-        <v>アイテム毎に専用設計された「しなやか高強力フロロリーダー」</v>
+        <v>專為烏賊金屬餌與鉛墜釣組設計、著重視認性的專用配色! / 專為烏賊金屬布捲釣法與鉛墜釣組設計、著重視認性的專用配色! / 為了讓與烏賊關聯的所有時間,都充滿感動。「EMERALDAS」。這是DAIWA率先於全球推出的烏賊遊戲專用綜合釣具品牌。為將烏賊帶入您手中。更為在迎接巔峰時刻前,與烏賊關聯的每分每秒,皆能充滿感動而存在。爽快的鉤組手感。從下落、停留到刺魚,在原本只需靜候的時光裡,持續傳遞變化與徵兆的靈敏度。即使與大魚搏鬥也能安心的可靠感。更因整體設計方能實現的快適操作感,以及在相機捲中格外出眾的攝影美感。EMERALDAS。自從握在手中的那一刻起,願隨時隨地,永遠獻上感動。</v>
       </c>
     </row>
     <row r="15">
@@ -897,10 +897,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="str">
-        <v>プレッソエリアデュラブラMAX PRESSO AREA DURABRAMAX</v>
+        <v>UVF月下美人DuraSensor+Si2</v>
       </c>
       <c r="D15" t="str">
-        <v/>
+        <v>UVF月下美人DuraSensor+Si2</v>
       </c>
       <c r="E15" t="str">
         <v/>
@@ -909,19 +909,19 @@
         <v/>
       </c>
       <c r="G15" t="str">
-        <v>Nylon</v>
+        <v>PE</v>
       </c>
       <c r="H15" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%E3%82%A8%E3%83%AA%E3%82%A2%E3%83%87%E3%83%A5%E3%83%A9%E3%83%96%E3%83%A9MAX%20PRESSO%20AREA%20DURABRAMAX_main.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BADuraSensor%2BSi2_main.jpg</v>
       </c>
       <c r="I15" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="J15" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="K15" t="str">
-        <v>耐摩耗性MAX、コスレに強いナイロンライン！</v>
+        <v>月之響進化為耐磨性優「DURA」。正因採用極細PE,方能實現高密度「肌肉PE」! / 「月之響」進化再登場!搭載卓越耐磨耗性的「DURA」技術。正因為是極細PE線,更需要高密度的「肌肉型PE」! / 夜裡綻放的花朵,持續綻放著更耀眼的光芒。2005年,DAIWA產品陣容首度登場的輕量海水遊戲專用釣具『月下美人』。猶如絢爛盛放的花朵,月下美人翩然起舞,釣友亦隨之躍動。月下美人釣具系列,專為應對近在咫尺卻需極致細膩手法的竹筴魚,以及藏身岩隙海藻縫隙、時刻戒備等待魚餌現身的老獪大型岩魚而進化。今後月下美人將持續與釣友共同進化,帶來前所未有的愉悅與樂趣。月下美人的絢麗光輝,將持續照亮輕海水釣場。</v>
       </c>
     </row>
     <row r="16">
@@ -932,10 +932,10 @@
         <v>2</v>
       </c>
       <c r="C16" t="str">
-        <v>プレッソ　エリア　TYPE-F PRESSO AREA TYPE F</v>
+        <v>D-FRON 船用子線</v>
       </c>
       <c r="D16" t="str">
-        <v/>
+        <v>D-FRON 船用子線</v>
       </c>
       <c r="E16" t="str">
         <v/>
@@ -947,16 +947,16 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H16" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%E3%80%80%E3%82%A8%E3%83%AA%E3%82%A2%E3%80%80TYPE-F%20PRESSO%20AREA%20TYPE%20F_PressoAreaTypeF_100.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/D-FRON%20%E8%88%B9%E7%94%A8%E5%AD%90%E7%B7%9A_main.png</v>
       </c>
       <c r="I16" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="J16" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="K16" t="str">
-        <v>エリアのスレたトラウトを攻略！ハイスペック、フロロカーボンライン！</v>
+        <v>值得信賴的氟碳線綁鉤子線「D-FRON船用綁鉤子線」全面升級 / 值得信賴的碳素線「D-FRON 船用子線」全新升級,性能再進化! / 適用於各類船釣的標準船用綁鉤子線。號數別柔韌處理。3號以下在保持柔韌性的同時,設定適度的張力。4號以上號數太號數,設定越為柔韌.具備優異耐久性的100%氟碳線。結節強力重視設計,結節強度高。比重:1.78。</v>
       </c>
     </row>
     <row r="17">
@@ -967,10 +967,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="str">
-        <v>プレッソ タイプN PRESSO TYPE N</v>
+        <v>磯SENSOR SS+Si</v>
       </c>
       <c r="D17" t="str">
-        <v/>
+        <v>磯SENSOR SS+Si</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -979,19 +979,19 @@
         <v/>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>PE</v>
       </c>
       <c r="H17" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%82%BF%E3%82%A4%E3%83%97N%20PRESSO%20TYPE%20N_PressoTypeN.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E7%A3%AFSENSOR%20SS%2BSi_main.jpg</v>
       </c>
       <c r="I17" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="J17" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="K17" t="str">
-        <v>低伸度設計で小さなバイトも見逃さない高感度！</v>
+        <v>張力強韌不易纏繞導環、操作順手的高比重PE岩岸母線 / 具備優異硬度、所以不易纏繞導環,且操作性能極佳的高比重磯釣PE母線。 / PE(4股)+PTFE的高比重PE釣線。高比重PE材質,因此抗風性強且不易產生表層波紋,排水性優異。講究的比重設定極盡可能接近尼龍材質,以提升操作便利性。號數造成的比重差異較小,可控制在比重1.10~1.20的範圍內。另一項堅持在於使整條釣線保持魚鉤,從而不易發生導環纏繞。因可使用細釣線,故即使輕型釣組亦能遠投.因釣線徑細,母線不易受多餘水流牽引,仕掛不易偏離目標水流。因魚訊能直接傳遞,可實現快速提竿,不易被魚吞入魚鉤。採用高辨識度的橘色,每三公尺設有引擎色標記。聚乙烯(PE)比重 1.10~1.20</v>
       </c>
     </row>
     <row r="18">
@@ -1002,10 +1002,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="str">
-        <v>UVFプレッソエリアデュラセンサー×8EX+Si3 UVF PRESSO AREA DURA SENSOR X8EX+SI3</v>
+        <v>ASTRON磯 TYPE-S SUSPEND</v>
       </c>
       <c r="D18" t="str">
-        <v/>
+        <v>ASTRON磯 TYPE-S SUSPEND</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1014,19 +1014,19 @@
         <v/>
       </c>
       <c r="G18" t="str">
-        <v>PE</v>
+        <v>Nylon</v>
       </c>
       <c r="H18" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%E3%82%A8%E3%83%AA%E3%82%A2%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC%C3%978EX%2BSi3%20UVF%20PRESSO%20AREA%20DURA%20SENSOR%20X8EX%2BSI3_main.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/ASTRON%E7%A3%AF%20TYPE-S%20SUSPEND_main.jpg</v>
       </c>
       <c r="I18" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="J18" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="K18" t="str">
-        <v>和田テスターこだわりの競技モデル！ハイスペック8ブレイド極細PEライン！</v>
+        <v>輕快的操作感。 / 半懸浮類型。特殊表面加工帶來輕快操作感。各性能均衡的全能型規格。釣線質順滑易操控,讓您無壓力地專注於釣魚。具備優異辨識度的「熱橙色」。不損及釣線性能的「平行繞線DPLS」。1.65~6號共計8品項。</v>
       </c>
     </row>
     <row r="19">
@@ -1037,10 +1037,10 @@
         <v>2</v>
       </c>
       <c r="C19" t="str">
-        <v>月下美人フロロリーダー GEKKABIJIN FLUORO LEADER</v>
+        <v>ASTRON 磯 MAX GAMMA2</v>
       </c>
       <c r="D19" t="str">
-        <v/>
+        <v>ASTRON 磯 MAX GAMMA2</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1049,19 +1049,19 @@
         <v/>
       </c>
       <c r="G19" t="str">
-        <v>Fluorocarbon</v>
+        <v>Nylon</v>
       </c>
       <c r="H19" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%E3%83%95%E3%83%AD%E3%83%AD%E3%83%AA%E3%83%BC%E3%83%80%E3%83%BC%20GEKKABIJIN%20FLUORO%20LEADER_GekkabijinFluoroLeader_Package1.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/ASTRON%20%E7%A3%AF%20MAX%20GAMMA2_main.jpg</v>
       </c>
       <c r="I19" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="J19" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="K19" t="str">
-        <v>月下美人リーダーが強くしなやかなになってパワーアップ。ライトゲーム全般をカバーするラインアップ。</v>
+        <v>耐磨性MAX的伽瑪系列!撥水性能的耐久性較傳統提升1.5倍! / 耐磨耗性極致巔峰-GAMMA 系列!防潑水性能持久度較前作大幅提升 1.5 倍! / 耐磨性MAX!抗磨損!(約為普通尼龍線的20倍)(本公司比)採用全新超撥水「UWRII加工」技術,撥水性能大幅提升且持久耐用。同時大幅減少釣竿沾黏現象。導線順暢,即使輕型仕掛也能提升飛距.不損及釣線性能的平行繞線DPLS。在視認性方面,透過特殊加工技術,大幅提升陽光下的辨識度。採用亮粉色標記便於掌握釣線動態與仕掛位置;海藍色標記則兼具水中隱蔽性與釣者視認性,整體採用高亮度色彩+標記設計,實現視覺辨識優化。</v>
       </c>
     </row>
     <row r="20">
@@ -1072,10 +1072,10 @@
         <v>2</v>
       </c>
       <c r="C20" t="str">
-        <v>プレッソ エリア TYPE-E PRESSO AREA TYPE-E</v>
+        <v>ASTRON 磯 MASTER EDITION TV</v>
       </c>
       <c r="D20" t="str">
-        <v/>
+        <v>ASTRON 磯 MASTER EDITION TV</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1084,19 +1084,19 @@
         <v/>
       </c>
       <c r="G20" t="str">
-        <v>Ester</v>
+        <v>Nylon</v>
       </c>
       <c r="H20" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%97%E3%83%AC%E3%83%83%E3%82%BD%20%E3%82%A8%E3%83%AA%E3%82%A2%20TYPE-E%20PRESSO%20AREA%20TYPE-E_PressoAreaTypeE.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/ASTRON%20%E7%A3%AF%20MASTER%20EDITION%20TV_main.jpg</v>
       </c>
       <c r="I20" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="J20" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="K20" t="str">
-        <v>高感度エステルライン</v>
+        <v>【長浮標頂端竟化為釣線!?】具備極高辨識度的競技用高平衡尼龍釣線!! / 【就像把長標棒形浮標的頂端變成了釣線!?】具備極致高辨識度的競技用高平衡尼龍線!! / 採用如長浮標頂端般的高辨識度色彩,能即時應對細微的魚訊。為追求更細號捕獲大魚,在追求高結節強度的同時,兼具高直線強度與耐磨損性,實現高平衡性的釣線。超強撥水(UWR加工)使撥水能力與持久力大幅提升!不僅解決了釣竿沾黏問題,更讓線組整理變得輕盈順手,操作極為輕鬆。號數別釣線質設計。細號數賦予張力,太號數則呈現易於操控的柔軟質感。懸浮於水面直下的懸浮類型。尼龍 比重 1.14</v>
       </c>
     </row>
     <row r="21">
@@ -1107,10 +1107,10 @@
         <v>2</v>
       </c>
       <c r="C21" t="str">
-        <v>UVF エメラルダスデュラセンサーX8EX+Si3 IM UVF EMERALDAS DURASENSOR X8EX+SI3 IM</v>
+        <v>FLUORO 子線 X’LINK</v>
       </c>
       <c r="D21" t="str">
-        <v/>
+        <v>FLUORO 子線 X’LINK</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1119,19 +1119,19 @@
         <v/>
       </c>
       <c r="G21" t="str">
-        <v/>
+        <v>Fluorocarbon</v>
       </c>
       <c r="H21" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E3%82%A8%E3%83%A1%E3%83%A9%E3%83%AB%E3%83%80%E3%82%B9%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BCX8EX%2BSi3%20IM%20UVF%20EMERALDAS%20DURASENSOR%20X8EX%2BSI3%20IM_4550133628382.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/FLUORO%20%E5%AD%90%E7%B7%9A%20X%E2%80%99LINK_main.jpg</v>
       </c>
       <c r="I21" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="J21" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="K21" t="str">
-        <v>視認性を重視したイカメタル・オモリグ専用カラー！</v>
+        <v>DAIWA最新科技誕生的「頂上氟碳線」。此乃最強。正是巔峰。 / DAIWA 最新科技打造「頂尖碳素線」。這就是最強,無庸置疑的巔峰。 / DAIWA獨家特殊樹脂原料「TOUGH RESIN」。強固連接分子間的架橋結構「X’LINK」。「NANO CONTROL」技術,充分發揮釣線特性。透過三項新技術的融合,實現DAIWA綁鉤子線史上最強的結節強度。適度的黏性與延展性,即使突然承受高負荷也不易斷裂。柔軟且易於處理。附有方便的號數分類彩色線杯帶。自然透明色與隱形藍的兩種顏色。平行卷DPLS。線杯採用海洋生物可分解樹脂「NEQAS OCEAN」。氟碳線 比重1.78</v>
       </c>
     </row>
     <row r="22">
@@ -1142,10 +1142,10 @@
         <v>2</v>
       </c>
       <c r="C22" t="str">
-        <v>紅牙フロロリーダーEX KOHGA FLUORO LEADER EX</v>
+        <v>銀狼LINE</v>
       </c>
       <c r="D22" t="str">
-        <v/>
+        <v>銀狼LINE</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1154,19 +1154,19 @@
         <v/>
       </c>
       <c r="G22" t="str">
-        <v>Fluorocarbon</v>
+        <v>Nylon</v>
       </c>
       <c r="H22" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E7%B4%85%E7%89%99%E3%83%95%E3%83%AD%E3%83%AD%E3%83%AA%E3%83%BC%E3%83%80%E3%83%BCEX%20KOHGA%20FLUORO%20LEADER%20EX_KOHGA_FLUOROLEADER_EX_package_ol.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E9%8A%80%E7%8B%BCLINE_main.jpg</v>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="J22" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="K22" t="str">
-        <v>タイラバ・テンヤ専用,高強力フロロリーダー,スプールバンド,ミディアムソフト,平行巻DPLS</v>
+        <v>兼具耐磨損性與柔韌性的黑鯛專用尼龍母線。 / 兼具耐磨性與柔韌性的黑鯛專用尼龍母線。 / 磨礪智慧,磨利利齒。銳利的目光、強韌的下顎,以及銀光閃閃的優美體軀⋯⋯。這副歷經百戰淬鍊的沉穩銀色身軀,恰似智謀超群的孤高狼群,因而誕生了專為黑鯛(鯛魚)浮標釣法設計的「銀狼」。與黑鯛(鯛魚)的生死較量,時而需大膽出擊,時而需狡黠周旋。要制勝這場搏鬥,釣者智慧與技藝相輔相成的頂尖釣具不可或缺。專注於黑鯛(鯛魚),執著於浮標釣法。為這般釣師獻上精心打造的專屬品項系列。為迎戰而備,銀狼今日亦在磨利獠牙。</v>
       </c>
     </row>
     <row r="23">
@@ -1177,10 +1177,10 @@
         <v>2</v>
       </c>
       <c r="C23" t="str">
-        <v>フロロショックリーダーX FLUORO SHOCK LEADER X</v>
+        <v>ASTRON 磯 GREAT EX2</v>
       </c>
       <c r="D23" t="str">
-        <v/>
+        <v>ASTRON 磯 GREAT EX2</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1189,19 +1189,19 @@
         <v/>
       </c>
       <c r="G23" t="str">
-        <v>Fluorocarbon</v>
+        <v>Nylon</v>
       </c>
       <c r="H23" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%95%E3%83%AD%E3%83%AD%E3%82%B7%E3%83%A7%E3%83%83%E3%82%AF%E3%83%AA%E3%83%BC%E3%83%80%E3%83%BCX%20FLUORO%20SHOCK%20LEADER%20X_FluoroShockLeaderX_Package.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/ASTRON%20%E7%A3%AF%20GREAT%20EX2_main.jpg</v>
       </c>
       <c r="I23" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="J23" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="K23" t="str">
-        <v>ライトゲームからジギングまで使える汎用フロロショックリーダー「X」誕生。</v>
+        <v>大和史上最強的釣線全面升級!以強韌的岩岸釣線將大魚收入掌中! / Daiwa史上最強母線!以強韌的磯釣母線,將大魚收入手中! / DPLS(平行捲線) 出廠時線圈上纏繞的釣線會施加挺度以利進行捲線。此時,若線體上下交疊,釣線會因受力導致局部扁平。為了避免這種強度下降,DPLS規格是採用平行捲線的方式,防止線體扁平,不損害釣線本身的性能。</v>
       </c>
     </row>
     <row r="24">
@@ -1212,10 +1212,10 @@
         <v>2</v>
       </c>
       <c r="C24" t="str">
-        <v>モアザンリーダーEX II TYPE-F（フロロ） morethan LEADER EX II TYPE-F（FLUORO）</v>
+        <v>D-FRON FLUORO 子線</v>
       </c>
       <c r="D24" t="str">
-        <v/>
+        <v>D-FRON FLUORO 子線</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1227,16 +1227,16 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H24" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%A2%E3%82%A2%E3%82%B6%E3%83%B3%E3%83%AA%E3%83%BC%E3%83%80%E3%83%BCEX%20II%20TYPE-F%EF%BC%88%E3%83%95%E3%83%AD%E3%83%AD%EF%BC%89%20morethan%20LEADER%20EX%20II%20TYPE-F%EF%BC%88FLUORO%EF%BC%89_MT_LeaderType-F2_NaturalClear.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/D-FRON%20FLUORO%20%E5%AD%90%E7%B7%9A_main.jpg</v>
       </c>
       <c r="I24" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="J24" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="K24" t="str">
-        <v>シーバス専用設計「高強力フロロカーボンリーダー」。便利な「スプールバンド」付き。</v>
+        <v>易於操控且柔韌萬能!高性價比氟碳線綁鉤子線 / 易於綁線且柔韌萬能!高性價比碳素子線 / 透過不同號數的線杯帶,不僅能輕鬆固定釣線,亦便於目視辨識線號。</v>
       </c>
     </row>
     <row r="25">
@@ -1247,10 +1247,10 @@
         <v>2</v>
       </c>
       <c r="C25" t="str">
-        <v>シルバークリーク TYPE-N（ナイロン） SILVER CREEK TYPE-N</v>
+        <v>SURF CASTER 力線</v>
       </c>
       <c r="D25" t="str">
-        <v/>
+        <v>SURF CASTER 力線</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1262,16 +1262,16 @@
         <v>Nylon</v>
       </c>
       <c r="H25" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%B7%E3%83%AB%E3%83%90%E3%83%BC%E3%82%AF%E3%83%AA%E3%83%BC%E3%82%AF%20TYPE-N%EF%BC%88%E3%83%8A%E3%82%A4%E3%83%AD%E3%83%B3%EF%BC%89%20SILVER%20CREEK%20TYPE-N_SilverCreekType-N.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/SURF%20CASTER%20%E5%8A%9B%E7%B7%9A_main.png</v>
       </c>
       <c r="I25" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="J25" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="K25" t="str">
-        <v>ネイティブトラウト専用ハイスペックナイロンライン。「リーダー付きコンセプト」メインライン。</v>
+        <v>不易打結且易於使用的拋投專用釣線 / 不易產生捲曲變型、好上手的沙岸拋投專用線。 / 耐磨耗性素材配合。柔軟的觸感能迅速消除釣線皺褶,使用起來相當順手。</v>
       </c>
     </row>
     <row r="26">
@@ -1282,10 +1282,10 @@
         <v>2</v>
       </c>
       <c r="C26" t="str">
-        <v>UVF ソルティガデュラセンサー8＋Si2 UVF SALTIGA DURA SENSOR×8＋Si2</v>
+        <v>D-FRON 船用子線 200FX</v>
       </c>
       <c r="D26" t="str">
-        <v/>
+        <v>D-FRON 船用子線 200FX</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1294,19 +1294,19 @@
         <v/>
       </c>
       <c r="G26" t="str">
-        <v/>
+        <v>Fluorocarbon</v>
       </c>
       <c r="H26" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E3%82%BD%E3%83%AB%E3%83%86%E3%82%A3%E3%82%AC%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC8%EF%BC%8BSi2%20UVF%20SALTIGA%20DURA%20SENSOR%C3%978%EF%BC%8BSi2_UVFSGDuraSensor8plusSi2.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/D-FRON%20%E8%88%B9%E7%94%A8%E5%AD%90%E7%B7%9A%20200FX_main.jpg</v>
       </c>
       <c r="I26" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="J26" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="K26" t="str">
-        <v>圧倒的耐摩耗性「デュラセンサー」。</v>
+        <v>大和船綁鉤子線系列中最柔韌的高強度氟碳線。 / DAIWA船用子線系列中最柔韌的氟素線。 / 高感度氟碳線100%釣線。船綁鉤子線系列中最靈活的設計。即使是太釣線也能輕鬆打結的柔韌線材。不易產生扭曲的大型線杯。結節強力重視設計。超值200公尺捲裝。顏色:自然色。</v>
       </c>
     </row>
     <row r="27">
@@ -1317,10 +1317,10 @@
         <v>2</v>
       </c>
       <c r="C27" t="str">
-        <v>ソルティガ フロロリーダー X’LINK（クロスリンク） SALTIGA FLUORO LEADER X’LINK</v>
+        <v>JUSTRON FLUORO</v>
       </c>
       <c r="D27" t="str">
-        <v/>
+        <v>JUSTRON FLUORO</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1332,27 +1332,27 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H27" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%BD%E3%83%AB%E3%83%86%E3%82%A3%E3%82%AC%20%E3%83%95%E3%83%AD%E3%83%AD%E3%83%AA%E3%83%BC%E3%83%80%E3%83%BC%20X%E2%80%99LINK%EF%BC%88%E3%82%AF%E3%83%AD%E3%82%B9%E3%83%AA%E3%83%B3%E3%82%AF%EF%BC%89%20SALTIGA%20FLUORO%20LEADER%20X%E2%80%99LINK_SG_FuluroLaederXLink.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/JUSTRON%20FLUORO_main.jpg</v>
       </c>
       <c r="I27" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="J27" t="str">
-        <v/>
+        <v>2026-05-02 08:28:32</v>
       </c>
       <c r="K27" t="str">
-        <v>ダイワの最新テクノロジーで新たに誕生した「頂上フロロ」。これが最強。まさに「頂上」。</v>
+        <v>萬用型大容量碳素線終於登場!用途無限大,滿足各種釣魚需求。 / JUSTRON 氟碳線終於登場。採用 100% 高強度氟碳纖維。柔韌設計,不易產生捲曲壓痕變形。用途無限廣泛:路亞黑鱸、滾釣、穴釣、船釣飄浮釣、輕型海水路亞、岩魚釣、各種子線、各種前導線、仕掛製作等。附帶便利的標記記號(300m 規格:每 100m 標記;240m 規格:每 80m 標記)。隱形粉紅:DAIWA 獨家開發,具備極高隱形效果的粉紅色。氟碳線比重 1.78</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>DLN1026</v>
+        <v>DLN1041</v>
       </c>
       <c r="B28">
         <v>2</v>
       </c>
       <c r="C28" t="str">
-        <v>UVF ソルティガ SJ デュラセンサー×8＋Si2 UVF SALTIGA DURA SENSOR×8＋Si2</v>
+        <v>モアザンリーダーEX II TYPE-N（ナイロン） morethan LEADER EX II TYPE-N（NYLON）</v>
       </c>
       <c r="D28" t="str">
         <v/>
@@ -1364,10 +1364,10 @@
         <v/>
       </c>
       <c r="G28" t="str">
-        <v/>
+        <v>Nylon</v>
       </c>
       <c r="H28" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E3%82%BD%E3%83%AB%E3%83%86%E3%82%A3%E3%82%AC%20SJ%20%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC%C3%978%EF%BC%8BSi2%20UVF%20SALTIGA%20DURA%20SENSOR%C3%978%EF%BC%8BSi2_SGSJDURA8P.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%A2%E3%82%A2%E3%82%B6%E3%83%B3%E3%83%AA%E3%83%BC%E3%83%80%E3%83%BCEX%20II%20TYPE-N%EF%BC%88%E3%83%8A%E3%82%A4%E3%83%AD%E3%83%B3%EF%BC%89%20morethan%20LEADER%20EX%20II%20TYPE-N%EF%BC%88NYLON%EF%BC%89_MT_LeaderType-N2_Clear.jpg</v>
       </c>
       <c r="I28" t="str">
         <v/>
@@ -1376,18 +1376,18 @@
         <v/>
       </c>
       <c r="K28" t="str">
-        <v>超高感度！！驚異の伸度3％未満！！異次元の感度を体感せよ！</v>
+        <v>シーバス専用設計「高強力ナイロンリーダー」。便利な「スプールバンド」付き。</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>DLN1027</v>
+        <v>DLN1042</v>
       </c>
       <c r="B29">
         <v>2</v>
       </c>
       <c r="C29" t="str">
-        <v>モアザンデュラブラ MAX MORETHAN DURABRA MAX</v>
+        <v>月下美人 TYPE-E 白 GEKKABIJIN TYPE-E HAKU</v>
       </c>
       <c r="D29" t="str">
         <v/>
@@ -1399,10 +1399,10 @@
         <v/>
       </c>
       <c r="G29" t="str">
-        <v>Nylon</v>
+        <v/>
       </c>
       <c r="H29" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%A2%E3%82%A2%E3%82%B6%E3%83%B3%E3%83%87%E3%83%A5%E3%83%A9%E3%83%96%E3%83%A9%20MAX%20MORETHAN%20DURABRA%20MAX_MORETHAN-DURABRA-MAX.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%20TYPE-E%20%E7%99%BD%20GEKKABIJIN%20TYPE-E%20HAKU_GekkabijinTypeE_Haku_Package.jpg</v>
       </c>
       <c r="I29" t="str">
         <v/>
@@ -1411,18 +1411,18 @@
         <v/>
       </c>
       <c r="K29" t="str">
-        <v>モアザン デュラブラ,デュラブラ,釣糸,釣り糸,ライン,ナイロン,モアザンデュラブラ</v>
+        <v>ライトリグの操作性と感度を重視した「NEW TYPE-E 白」。白（ハク）カラーでラインからの情報量アップ＆操作性向上。</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>DLN1028</v>
+        <v>DLN1043</v>
       </c>
       <c r="B30">
         <v>2</v>
       </c>
       <c r="C30" t="str">
-        <v>UVF モアザン デュラセンサー×8＋Si² UVF MORETHAN DURASENSOR X8BRAID +Si²</v>
+        <v>渓流ガンマ KEIRYU GAMMA</v>
       </c>
       <c r="D30" t="str">
         <v/>
@@ -1434,10 +1434,10 @@
         <v/>
       </c>
       <c r="G30" t="str">
-        <v>PE</v>
+        <v>Nylon</v>
       </c>
       <c r="H30" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E3%83%A2%E3%82%A2%E3%82%B6%E3%83%B3%20%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC%C3%978%EF%BC%8BSi%C2%B2%20UVF%20MORETHAN%20DURASENSOR%20X8BRAID%20%2BSi%C2%B2_UVF_MT_DuraSensor8BraidPlusSi2.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E6%B8%93%E6%B5%81%E3%82%AC%E3%83%B3%E3%83%9E%20KEIRYU%20GAMMA_KeiryuGamma.jpg</v>
       </c>
       <c r="I30" t="str">
         <v/>
@@ -1446,18 +1446,18 @@
         <v/>
       </c>
       <c r="K30" t="str">
-        <v>信頼のモアザン×8が圧倒的耐摩耗性「デュラセンサー」にパワーアップ。</v>
+        <v>コスレに強い！耐摩耗性5倍！（当社比）高強力ナイロンライン！</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>DLN1029</v>
+        <v>DLN1044</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
       <c r="C31" t="str">
-        <v>UVF ソルティガデュラセンサー×12EX+Si3 UVF SALTIGA DURA SENSOR×12EX+Si3</v>
+        <v>テンカラ テーパーライン TENKARA TAPER LINE</v>
       </c>
       <c r="D31" t="str">
         <v/>
@@ -1469,10 +1469,10 @@
         <v/>
       </c>
       <c r="G31" t="str">
-        <v>PE</v>
+        <v>Nylon</v>
       </c>
       <c r="H31" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E3%82%BD%E3%83%AB%E3%83%86%E3%82%A3%E3%82%AC%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC%C3%9712EX%2BSi3%20UVF%20SALTIGA%20DURA%20SENSOR%C3%9712EX%2BSi3_SALTIGA-DURASENSOR-12EX.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%86%E3%83%B3%E3%82%AB%E3%83%A9%20%E3%83%86%E3%83%BC%E3%83%91%E3%83%BC%E3%83%A9%E3%82%A4%E3%83%B3%20TENKARA%20TAPER%20LINE_TenkaraTaperLine.jpg</v>
       </c>
       <c r="I31" t="str">
         <v/>
@@ -1481,18 +1481,18 @@
         <v/>
       </c>
       <c r="K31" t="str">
-        <v>キャスティング専用PEラインが遂に登場。最上級の滑らかさと強さでBREAK YOUR RECORD！</v>
+        <v>レベルラインの軽さとテーパーラインの振り込みやすさを兼備したナイロン製モノテーパーライン</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>DLN1030</v>
+        <v>DLN1045</v>
       </c>
       <c r="B32">
         <v>2</v>
       </c>
       <c r="C32" t="str">
-        <v>UVF月下美人デュラセンサー＋Si² UVF GEKKABIJIN DURA SENSOR＋Si²</v>
+        <v>タフロン テンカラレベルライン TOUGHRON TENKARA LEVEL</v>
       </c>
       <c r="D32" t="str">
         <v/>
@@ -1504,10 +1504,10 @@
         <v/>
       </c>
       <c r="G32" t="str">
-        <v>PE</v>
+        <v/>
       </c>
       <c r="H32" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC%EF%BC%8BSi%C2%B2%20UVF%20GEKKABIJIN%20DURA%20SENSOR%EF%BC%8BSi%C2%B2_UVFGekkabijinDuraSensorSi2.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%BF%E3%83%95%E3%83%AD%E3%83%B3%20%E3%83%86%E3%83%B3%E3%82%AB%E3%83%A9%E3%83%AC%E3%83%99%E3%83%AB%E3%83%A9%E3%82%A4%E3%83%B3%20TOUGHRON%20TENKARA%20LEVEL_ToughronTenkaraLevelLine.jpg</v>
       </c>
       <c r="I32" t="str">
         <v/>
@@ -1516,18 +1516,18 @@
         <v/>
       </c>
       <c r="K32" t="str">
-        <v>月ノ響が耐摩耗性に優れた「DURA」へ進化。極細PEだからこそ、高密度「マッスルPE」！</v>
+        <v>毛バリを自然に流しやすいテンカラ用ライン</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>DLN1031</v>
+        <v>DLN1046</v>
       </c>
       <c r="B33">
         <v>2</v>
       </c>
       <c r="C33" t="str">
-        <v>ソルティガ ナイロンリーダー SALTIGA NYLON LEADER</v>
+        <v>UVF 月下美人デュラヘビー×4＋1＋Si2 UVF GEKKABIJIN DURAHEAVY×4＋1＋Si2</v>
       </c>
       <c r="D33" t="str">
         <v/>
@@ -1539,10 +1539,10 @@
         <v/>
       </c>
       <c r="G33" t="str">
-        <v>Nylon</v>
+        <v>PE</v>
       </c>
       <c r="H33" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%BD%E3%83%AB%E3%83%86%E3%82%A3%E3%82%AC%20%E3%83%8A%E3%82%A4%E3%83%AD%E3%83%B3%E3%83%AA%E3%83%BC%E3%83%80%E3%83%BC%20SALTIGA%20NYLON%20LEADER_SG_NylonLaeder40LB.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%E3%83%87%E3%83%A5%E3%83%A9%E3%83%98%E3%83%93%E3%83%BC%C3%974%EF%BC%8B1%EF%BC%8BSi2%20UVF%20GEKKABIJIN%20DURAHEAVY%C3%974%EF%BC%8B1%EF%BC%8BSi2_UVF_GekkaBijinPeDuraHeavy4_1_Si2.jpg</v>
       </c>
       <c r="I33" t="str">
         <v/>
@@ -1551,21 +1551,21 @@
         <v/>
       </c>
       <c r="K33" t="str">
-        <v>結節強力を徹底追及。リーダーに必要不可欠な「強さ」と「クッション性」をハイレベルに融合。</v>
+        <v>ライトゲーム用PEラインに高比重タイプが登場</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>DLN1032</v>
+        <v>SLN1000</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C34" t="str">
-        <v>月下美人TYPE-E 鋭感（エイカン） GEKKABIJIN TYPE-E EIKAN</v>
+        <v>Tanatoru 8</v>
       </c>
       <c r="D34" t="str">
-        <v/>
+        <v>Tanatoru 8</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1574,33 +1574,33 @@
         <v/>
       </c>
       <c r="G34" t="str">
-        <v/>
+        <v>PE</v>
       </c>
       <c r="H34" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BATYPE-E%20%E9%8B%AD%E6%84%9F%EF%BC%88%E3%82%A8%E3%82%A4%E3%82%AB%E3%83%B3%EF%BC%89%20GEKKABIJIN%20TYPE-E%20EIKAN_GekkaTypeE_Eikan.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Tanatoru%208_main.jpeg</v>
       </c>
       <c r="I34" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J34" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K34" t="str">
-        <v>鋭く感じ、多くの情報を掴む</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>DLN1033</v>
+        <v>SLN1001</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35" t="str">
-        <v>月下美人 TYPE-F 陽/陰 GEKKABIJIN TYPE-F YOU/IN</v>
+        <v>Tanatoru 4 / 8 100m 连盘</v>
       </c>
       <c r="D35" t="str">
-        <v/>
+        <v>Tanatoru 4 / 8 100m 连盘</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1609,33 +1609,33 @@
         <v/>
       </c>
       <c r="G35" t="str">
-        <v/>
+        <v>PE</v>
       </c>
       <c r="H35" t="str">
-        <v>images/daiwa_lines/月下美人 TYPE-F 陽陰 GEKKABIJIN TYPE-F YOUIN_Gekka_TypeF_Yo.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Tanatoru%204%20_%208%20100m%20%E8%BF%9E%E7%9B%98_main.jpeg</v>
       </c>
       <c r="I35" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J35" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K35" t="str">
-        <v>陽（ヨウ/サイトオレンジ）と陰（イン/ナチュラルクリア）を使い分けて釣果アップ！</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>DLN1034</v>
+        <v>SLN1002</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C36" t="str">
-        <v>エメラルダスオモリグリーダー EMERALDAS OMORIG LEADER</v>
+        <v>PITBULL G9</v>
       </c>
       <c r="D36" t="str">
-        <v/>
+        <v>PITBULL G9</v>
       </c>
       <c r="E36" t="str">
         <v/>
@@ -1644,33 +1644,33 @@
         <v/>
       </c>
       <c r="G36" t="str">
-        <v/>
+        <v>PE</v>
       </c>
       <c r="H36" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%A8%E3%83%A1%E3%83%A9%E3%83%AB%E3%83%80%E3%82%B9%E3%82%AA%E3%83%A2%E3%83%AA%E3%82%B0%E3%83%AA%E3%83%BC%E3%83%80%E3%83%BC%20EMERALDAS%20OMORIG%20LEADER_omorig-leader_4550133408427_data.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%20G9_main.jpeg</v>
       </c>
       <c r="I36" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J36" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K36" t="str">
-        <v>「スペクトロンセンサー」採用のオモリグ専用ライン</v>
+        <v>通过在柔韧的8股编织质感中加入高比重核心,在保持强度的同时,将PE线调校为沉水规格。适合追求直线强度和操作性的技术型钓手的结构设计。</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>DLN1035</v>
+        <v>SLN1003</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C37" t="str">
-        <v>HRF® ロックフィッシュフロロ HRF® ROCKFISH FLUORO</v>
+        <v>OCEA PLUGGER NYLON LEADER</v>
       </c>
       <c r="D37" t="str">
-        <v/>
+        <v>OCEA PLUGGER NYLON LEADER</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1679,33 +1679,33 @@
         <v/>
       </c>
       <c r="G37" t="str">
-        <v>Fluorocarbon</v>
+        <v>Nylon</v>
       </c>
       <c r="H37" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/HRF%C2%AE%20%E3%83%AD%E3%83%83%E3%82%AF%E3%83%95%E3%82%A3%E3%83%83%E3%82%B7%E3%83%A5%E3%83%95%E3%83%AD%E3%83%AD%20HRF%C2%AE%20ROCKFISH%20FLUORO_HRFRockFishFluoro.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%20PLUGGER%20NYLON%20LEADER_main.jpeg</v>
       </c>
       <c r="I37" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J37" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K37" t="str">
-        <v>ストラクチャーを果敢に攻めろ！ 強靭･しなやかフロロライン！</v>
+        <v>这是一款专为船上假饵钓、追求易用性而设计的尼龙前导线。特别注重提升使用感的柔韧性。打结时更容易收紧,且不易产生线卷记忆。抛投时通过导环也非常顺畅。柔韧的同时,在搏鱼过程中不会过度延展,能稳稳支撑。强度方面也十分讲究,不仅在全新状态下表现出色,还考虑到使用过程中因吸水导致的性能下降。采用不易被鱼察觉的透明色。</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>DLN1036</v>
+        <v>SLN1004</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C38" t="str">
-        <v>UVF 紅牙 デュラセンサー×8＋Si2 UVF KOGA DURA SENSOR×8＋Si2</v>
+        <v>PITBULL FLUORO LEADER</v>
       </c>
       <c r="D38" t="str">
-        <v/>
+        <v>PITBULL FLUORO LEADER</v>
       </c>
       <c r="E38" t="str">
         <v/>
@@ -1714,33 +1714,33 @@
         <v/>
       </c>
       <c r="G38" t="str">
-        <v>PE</v>
+        <v>Fluorocarbon</v>
       </c>
       <c r="H38" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E7%B4%85%E7%89%99%20%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC%C3%978%EF%BC%8BSi2%20UVF%20KOGA%20DURA%20SENSOR%C3%978%EF%BC%8BSi2_UVFKohgaDurasensor8Braid_1.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%20FLUORO%20LEADER_main.jpeg</v>
       </c>
       <c r="I38" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J38" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K38" t="str">
-        <v>ついに８ブレイドでも登場！！　TOUGH PE×Si2＝耐摩耗性300％以上（当社比）　ハイスペック＆低価格PE！！</v>
+        <v>采用高纯度氟碳原料并且日本制,单层结构设计。兼具强度与柔韧性,专为PITBULL系列打造的前导线。</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>DLN1037</v>
+        <v>SLN1005</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C39" t="str">
-        <v>タチメタルEX SG TACHIMETAL EX SEAGREEN</v>
+        <v>OCEA 17+</v>
       </c>
       <c r="D39" t="str">
-        <v/>
+        <v>OCEA 17+</v>
       </c>
       <c r="E39" t="str">
         <v/>
@@ -1749,33 +1749,33 @@
         <v/>
       </c>
       <c r="G39" t="str">
-        <v/>
+        <v>PE</v>
       </c>
       <c r="H39" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%BF%E3%83%81%E3%83%A1%E3%82%BF%E3%83%ABEX%20SG%20TACHIMETAL%20EX%20SEAGREEN_TACHIMETAL-EX-SEAGREEN.png</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%2017%2B_main.jpeg</v>
       </c>
       <c r="I39" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J39" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K39" t="str">
-        <v>ソルトルアー用リーダー,タチウオ,メタルライン,太刀メタル</v>
+        <v>采用16根鞘线和1根芯线的17根编线的结构,提供优秀的抛投手感,且拉力强度超越了OECA 8。OCEA 17+ PE采用了IZANAS的新系列SF700。</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>DLN1038</v>
+        <v>SLN1006</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" t="str">
-        <v>ベイトキャスティングデュラセンサー×12EX+Si3 BAIT CASTING DURA SENSOR X 12EX+SI3</v>
+        <v>OCEA 8</v>
       </c>
       <c r="D40" t="str">
-        <v/>
+        <v>OCEA 8</v>
       </c>
       <c r="E40" t="str">
         <v/>
@@ -1787,30 +1787,30 @@
         <v>PE</v>
       </c>
       <c r="H40" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%99%E3%82%A4%E3%83%88%E3%82%AD%E3%83%A3%E3%82%B9%E3%83%86%E3%82%A3%E3%83%B3%E3%82%B0%E3%83%87%E3%83%A5%E3%83%A9%E3%82%BB%E3%83%B3%E3%82%B5%E3%83%BC%C3%9712EX%2BSi3%20BAIT%20CASTING%20DURA%20SENSOR%20X%2012EX%2BSI3_BAIT_CASTING_DURA_SENSOR.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%208_main.jpeg</v>
       </c>
       <c r="I40" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J40" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K40" t="str">
-        <v>ベイトキャスティングに特化した専用PEライン！ライントラブルを減らし飛距離アップ！</v>
+        <v>对应超大型平政鱼/巨大金枪鱼,采用新原线X-Filament,并且施加了耐热性优秀的特殊硅树脂涂层,和普通渔线相比热传导率下降约1/4,另外顺滑性也有所提升。(4~12号)EX8首次使用TOUGH CORSS工法和均匀编织构造的VT工法,两者相结合拥有更强力的稳定感,Casting /Jigging平衡性优秀!顺滑性和硬度的平衡通过实战来验证,经过多次试钓,发现能有效减少缠导环(试用者提供的报告)。</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>DLN1039</v>
+        <v>SLN1007</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C41" t="str">
-        <v>月下美人 TYPE-N 煌 GEKKABIJIN TYPE-N KIRAMEKI</v>
+        <v>OCEA JIGGER MX4</v>
       </c>
       <c r="D41" t="str">
-        <v/>
+        <v>OCEA JIGGER MX4</v>
       </c>
       <c r="E41" t="str">
         <v/>
@@ -1819,33 +1819,33 @@
         <v/>
       </c>
       <c r="G41" t="str">
-        <v>Nylon</v>
+        <v>PE</v>
       </c>
       <c r="H41" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%20TYPE-N%20%E7%85%8C%20GEKKABIJIN%20TYPE-N%20KIRAMEKI_Gekka_TypeN_Kou.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%20JIGGER%20MX4_main.jpeg</v>
       </c>
       <c r="I41" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J41" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K41" t="str">
-        <v>UWR加工（ウルトラ撥水加工）で飛距離アップ！ロッドにベタツキもなく操作性向上！しなやか＆高感度ナイロンライン！煌くラインで軽快に操る！</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>DLN1040</v>
+        <v>SLN1008</v>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" t="str">
-        <v>テンカラ フライライン Y TENKARA FLYLINE Y</v>
+        <v>KISU SPECIAL EX4</v>
       </c>
       <c r="D42" t="str">
-        <v/>
+        <v>KISU SPECIAL EX4</v>
       </c>
       <c r="E42" t="str">
         <v/>
@@ -1854,33 +1854,33 @@
         <v/>
       </c>
       <c r="G42" t="str">
-        <v/>
+        <v>PE</v>
       </c>
       <c r="H42" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%86%E3%83%B3%E3%82%AB%E3%83%A9%20%E3%83%95%E3%83%A9%E3%82%A4%E3%83%A9%E3%82%A4%E3%83%B3%20Y%20TENKARA%20FLYLINE%20Y_TenkaraFryLineY.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/KISU%20SPECIAL%20EX4_main.jpeg</v>
       </c>
       <c r="I42" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J42" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K42" t="str">
-        <v>テンカラ専用のフライライン。初心者でも扱いやすいフローティングタイプ。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>DLN1041</v>
+        <v>SLN1009</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43" t="str">
-        <v>モアザンリーダーEX II TYPE-N（ナイロン） morethan LEADER EX II TYPE-N（NYLON）</v>
+        <v>KISU SPECIAL G5</v>
       </c>
       <c r="D43" t="str">
-        <v/>
+        <v>KISU SPECIAL G5</v>
       </c>
       <c r="E43" t="str">
         <v/>
@@ -1889,33 +1889,33 @@
         <v/>
       </c>
       <c r="G43" t="str">
-        <v>Nylon</v>
+        <v>PE</v>
       </c>
       <c r="H43" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%A2%E3%82%A2%E3%82%B6%E3%83%B3%E3%83%AA%E3%83%BC%E3%83%80%E3%83%BCEX%20II%20TYPE-N%EF%BC%88%E3%83%8A%E3%82%A4%E3%83%AD%E3%83%B3%EF%BC%89%20morethan%20LEADER%20EX%20II%20TYPE-N%EF%BC%88NYLON%EF%BC%89_MT_LeaderType-N2_Clear.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/KISU%20SPECIAL%20G5_main.jpeg</v>
       </c>
       <c r="I43" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J43" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K43" t="str">
-        <v>シーバス専用設計「高強力ナイロンリーダー」。便利な「スプールバンド」付き。</v>
+        <v>高比重PTEE纤维4编的高比重远投PE线,抛投时不易挂线,线也不易被浪冲走。</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>DLN1042</v>
+        <v>SLN1010</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C44" t="str">
-        <v>月下美人 TYPE-E 白 GEKKABIJIN TYPE-E HAKU</v>
+        <v>OCEA EX 前导线</v>
       </c>
       <c r="D44" t="str">
-        <v/>
+        <v>OCEA EX 前导线</v>
       </c>
       <c r="E44" t="str">
         <v/>
@@ -1924,33 +1924,33 @@
         <v/>
       </c>
       <c r="G44" t="str">
-        <v/>
+        <v>Fluorocarbon</v>
       </c>
       <c r="H44" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%20TYPE-E%20%E7%99%BD%20GEKKABIJIN%20TYPE-E%20HAKU_GekkabijinTypeE_Haku_Package.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%20EX%20%E5%89%8D%E5%AF%BC%E7%BA%BF_main.jpeg</v>
       </c>
       <c r="I44" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J44" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K44" t="str">
-        <v>ライトリグの操作性と感度を重視した「NEW TYPE-E 白」。白（ハク）カラーでラインからの情報量アップ＆操作性向上。</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>DLN1043</v>
+        <v>SLN1011</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C45" t="str">
-        <v>渓流ガンマ KEIRYU GAMMA</v>
+        <v>LIMITED PRO G5+ PE</v>
       </c>
       <c r="D45" t="str">
-        <v/>
+        <v>LIMITED PRO G5+ PE</v>
       </c>
       <c r="E45" t="str">
         <v/>
@@ -1959,33 +1959,33 @@
         <v/>
       </c>
       <c r="G45" t="str">
-        <v>Nylon</v>
+        <v>PE</v>
       </c>
       <c r="H45" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E6%B8%93%E6%B5%81%E3%82%AC%E3%83%B3%E3%83%9E%20KEIRYU%20GAMMA_KeiryuGamma.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/LIMITED%20PRO%20G5%2B%20PE_main.jpeg</v>
       </c>
       <c r="I45" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J45" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K45" t="str">
-        <v>コスレに強い！耐摩耗性5倍！（当社比）高強力ナイロンライン！</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>DLN1044</v>
+        <v>SLN1012</v>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46" t="str">
-        <v>テンカラ テーパーライン TENKARA TAPER LINE</v>
+        <v>PITBULL 12</v>
       </c>
       <c r="D46" t="str">
-        <v/>
+        <v>PITBULL 12</v>
       </c>
       <c r="E46" t="str">
         <v/>
@@ -1994,33 +1994,33 @@
         <v/>
       </c>
       <c r="G46" t="str">
-        <v>Nylon</v>
+        <v>PE</v>
       </c>
       <c r="H46" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%83%86%E3%83%B3%E3%82%AB%E3%83%A9%20%E3%83%86%E3%83%BC%E3%83%91%E3%83%BC%E3%83%A9%E3%82%A4%E3%83%B3%20TENKARA%20TAPER%20LINE_TenkaraTaperLine.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%2012_main.jpeg</v>
       </c>
       <c r="I46" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J46" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K46" t="str">
-        <v>レベルラインの軽さとテーパーラインの振り込みやすさを兼備したナイロン製モノテーパーライン</v>
+        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>DLN1045</v>
+        <v>SLN1013</v>
       </c>
       <c r="B47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C47" t="str">
-        <v>タフロン テンカラレベルライン TOUGHRON TENKARA LEVEL</v>
+        <v>HARDBULL 8+</v>
       </c>
       <c r="D47" t="str">
-        <v/>
+        <v>HARDBULL 8+</v>
       </c>
       <c r="E47" t="str">
         <v/>
@@ -2029,33 +2029,33 @@
         <v/>
       </c>
       <c r="G47" t="str">
-        <v/>
+        <v>PE</v>
       </c>
       <c r="H47" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/%E3%82%BF%E3%83%95%E3%83%AD%E3%83%B3%20%E3%83%86%E3%83%B3%E3%82%AB%E3%83%A9%E3%83%AC%E3%83%99%E3%83%AB%E3%83%A9%E3%82%A4%E3%83%B3%20TOUGHRON%20TENKARA%20LEVEL_ToughronTenkaraLevelLine.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/HARDBULL%208%2B_main.jpeg</v>
       </c>
       <c r="I47" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J47" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K47" t="str">
-        <v>毛バリを自然に流しやすいテンカラ用ライン</v>
+        <v>和PITBULL并列的PE线新系列。采用Honeywell公司的Spectra®材料,用MX2工法完成的8编线,提升了耐磨性。无论是纺车轮还是两轴轮都很适用。</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>DLN1046</v>
+        <v>SLN1014</v>
       </c>
       <c r="B48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C48" t="str">
-        <v>UVF 月下美人デュラヘビー×4＋1＋Si2 UVF GEKKABIJIN DURAHEAVY×4＋1＋Si2</v>
+        <v>GRAPPLER 8</v>
       </c>
       <c r="D48" t="str">
-        <v/>
+        <v>GRAPPLER 8</v>
       </c>
       <c r="E48" t="str">
         <v/>
@@ -2067,30 +2067,30 @@
         <v>PE</v>
       </c>
       <c r="H48" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/daiwa_lines/UVF%20%E6%9C%88%E4%B8%8B%E7%BE%8E%E4%BA%BA%E3%83%87%E3%83%A5%E3%83%A9%E3%83%98%E3%83%93%E3%83%BC%C3%974%EF%BC%8B1%EF%BC%8BSi2%20UVF%20GEKKABIJIN%20DURAHEAVY%C3%974%EF%BC%8B1%EF%BC%8BSi2_UVF_GekkaBijinPeDuraHeavy4_1_Si2.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/GRAPPLER%208_main.jpeg</v>
       </c>
       <c r="I48" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J48" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K48" t="str">
-        <v>ライトゲーム用PEラインに高比重タイプが登場</v>
+        <v>磨耗后也有强大的维持率,接近新品94%。(0.8号,公司内部测试)世界通用的优秀渔线。从GRAPPLER的概念中诞生的GRAPPLER 8,有着强力的上拉能力,搏鱼时的耐热性都得以提升。无论是栓饵还是铁板,或者是鲷鱼钓,各种钓法都可以应对。</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>SLN1000</v>
+        <v>SLN1015</v>
       </c>
       <c r="B49">
         <v>1</v>
       </c>
       <c r="C49" t="str">
-        <v>Tanatoru 8</v>
+        <v>KISU SPECIAL EX4 13m</v>
       </c>
       <c r="D49" t="str">
-        <v/>
+        <v>KISU SPECIAL EX4 13m</v>
       </c>
       <c r="E49" t="str">
         <v/>
@@ -2102,30 +2102,30 @@
         <v>PE</v>
       </c>
       <c r="H49" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Tanatoru%208_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/KISU%20SPECIAL%20EX4%2013m_main.jpeg</v>
       </c>
       <c r="I49" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J49" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K49" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>在比赛时全力抛投也能承受住,面对强大的力量游刃有余。</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>SLN1001</v>
+        <v>SLN1016</v>
       </c>
       <c r="B50">
         <v>1</v>
       </c>
       <c r="C50" t="str">
-        <v>Tanatoru 4 / 8 100m  连盘</v>
+        <v>Tanatoru 4</v>
       </c>
       <c r="D50" t="str">
-        <v/>
+        <v>Tanatoru 4</v>
       </c>
       <c r="E50" t="str">
         <v/>
@@ -2137,13 +2137,13 @@
         <v>PE</v>
       </c>
       <c r="H50" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Tanatoru%204%20_%208%20100m%20%20%E8%BF%9E%E7%9B%98_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Tanatoru%204_main.jpeg</v>
       </c>
       <c r="I50" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J50" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K50" t="str">
         <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
@@ -2151,16 +2151,16 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>SLN1002</v>
+        <v>SLN1017</v>
       </c>
       <c r="B51">
         <v>1</v>
       </c>
       <c r="C51" t="str">
-        <v>PITBULL G9</v>
+        <v>KAIKON</v>
       </c>
       <c r="D51" t="str">
-        <v/>
+        <v>KAIKON</v>
       </c>
       <c r="E51" t="str">
         <v/>
@@ -2169,33 +2169,33 @@
         <v/>
       </c>
       <c r="G51" t="str">
-        <v>PE</v>
+        <v>Nylon</v>
       </c>
       <c r="H51" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%20G9_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/KAIKON_main.jpeg</v>
       </c>
       <c r="I51" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J51" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K51" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>延展性、硬度、耐磨耗性、打结容易度等方面做好平衡的石鲷用线,考虑到近距离钓所以采用了棕色配色。</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>SLN1003</v>
+        <v>SLN1018</v>
       </c>
       <c r="B52">
         <v>1</v>
       </c>
       <c r="C52" t="str">
-        <v>OCEA PLUGGER NYLON LEADER</v>
+        <v>BULL'S EYE 远投</v>
       </c>
       <c r="D52" t="str">
-        <v/>
+        <v>BULL'S EYE 远投</v>
       </c>
       <c r="E52" t="str">
         <v/>
@@ -2207,30 +2207,30 @@
         <v>Nylon</v>
       </c>
       <c r="H52" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%20PLUGGER%20NYLON%20LEADER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BULL'S%20EYE%20%E8%BF%9C%E6%8A%95_main.jpeg</v>
       </c>
       <c r="I52" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J52" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K52" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>延展性高的远投专用尼龙线,通过延展性来应对目标鱼的急冲,通过粘性来攻略。采用荧光绿,实现了高识别性。</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>SLN1004</v>
+        <v>SLN1019</v>
       </c>
       <c r="B53">
         <v>1</v>
       </c>
       <c r="C53" t="str">
-        <v>PITBULL FLUORO LEADER</v>
+        <v>OCEA JIGGER MASTER 前导线</v>
       </c>
       <c r="D53" t="str">
-        <v/>
+        <v>OCEA JIGGER MASTER 前导线</v>
       </c>
       <c r="E53" t="str">
         <v/>
@@ -2242,30 +2242,30 @@
         <v>Fluorocarbon</v>
       </c>
       <c r="H53" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%20FLUORO%20LEADER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%20JIGGER%20MASTER%20%E5%89%8D%E5%AF%BC%E7%BA%BF_main.jpeg</v>
       </c>
       <c r="I53" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J53" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K53" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>采用强度优秀、超高分子量的氟碳素材!和以前的OCEA前导线相比,实现了更高等级的「柔软度」と「冲击吸收性」,测试过程中,多个记录都是这款渔线创造的。线不易打结或晃动,适合长时间使用。在线杯上线时也更适合,推荐搭配慢摇的回转铁板使用。采用两重构造!外层柔软构造让线的打结强度更稳定且强力,内芯坚固让你搏鱼时更能坚持住,依靠粘性攻略目标。</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>SLN1005</v>
+        <v>SLN1020</v>
       </c>
       <c r="B54">
         <v>1</v>
       </c>
       <c r="C54" t="str">
-        <v>OCEA 17+</v>
+        <v>Sephia 8+</v>
       </c>
       <c r="D54" t="str">
-        <v/>
+        <v>Sephia 8+</v>
       </c>
       <c r="E54" t="str">
         <v/>
@@ -2277,13 +2277,13 @@
         <v>PE</v>
       </c>
       <c r="H54" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%2017%2B_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Sephia%208%2B_main.jpeg</v>
       </c>
       <c r="I54" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J54" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K54" t="str">
         <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
@@ -2291,16 +2291,16 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>SLN1006</v>
+        <v>SLN1021</v>
       </c>
       <c r="B55">
         <v>1</v>
       </c>
       <c r="C55" t="str">
-        <v>OCEA 8</v>
+        <v>PITBULL 8+</v>
       </c>
       <c r="D55" t="str">
-        <v/>
+        <v>PITBULL 8+</v>
       </c>
       <c r="E55" t="str">
         <v/>
@@ -2312,13 +2312,13 @@
         <v>PE</v>
       </c>
       <c r="H55" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%208_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%208%2B_main.jpeg</v>
       </c>
       <c r="I55" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J55" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K55" t="str">
         <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
@@ -2326,16 +2326,16 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>SLN1007</v>
+        <v>SLN1022</v>
       </c>
       <c r="B56">
         <v>1</v>
       </c>
       <c r="C56" t="str">
-        <v>OCEA JIGGER MX4</v>
+        <v>FUKASE 船</v>
       </c>
       <c r="D56" t="str">
-        <v/>
+        <v>FUKASE 船</v>
       </c>
       <c r="E56" t="str">
         <v/>
@@ -2344,16 +2344,16 @@
         <v/>
       </c>
       <c r="G56" t="str">
-        <v>PE</v>
+        <v>Ester</v>
       </c>
       <c r="H56" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%20JIGGER%20MX4_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/FUKASE%20%E8%88%B9_main.jpeg</v>
       </c>
       <c r="I56" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J56" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K56" t="str">
         <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
@@ -2361,16 +2361,16 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>SLN1008</v>
+        <v>SLN1023</v>
       </c>
       <c r="B57">
         <v>1</v>
       </c>
       <c r="C57" t="str">
-        <v>KISU SPECIAL EX4</v>
+        <v>Sephia G5</v>
       </c>
       <c r="D57" t="str">
-        <v/>
+        <v>Sephia G5</v>
       </c>
       <c r="E57" t="str">
         <v/>
@@ -2382,13 +2382,13 @@
         <v>PE</v>
       </c>
       <c r="H57" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/KISU%20SPECIAL%20EX4%2013m_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Sephia%20G5_main.jpeg</v>
       </c>
       <c r="I57" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J57" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K57" t="str">
         <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
@@ -2396,16 +2396,16 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>SLN1009</v>
+        <v>SLN1024</v>
       </c>
       <c r="B58">
         <v>1</v>
       </c>
       <c r="C58" t="str">
-        <v>KISU SPECIAL G5</v>
+        <v>Sephia 8</v>
       </c>
       <c r="D58" t="str">
-        <v/>
+        <v>Sephia 8</v>
       </c>
       <c r="E58" t="str">
         <v/>
@@ -2417,30 +2417,30 @@
         <v>PE</v>
       </c>
       <c r="H58" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/KISU%20SPECIAL%20G5_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Sephia%208_main.jpeg</v>
       </c>
       <c r="I58" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J58" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K58" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>减少导环噪音。 顺滑的表面工艺减少了导环噪音。提升顺滑度 致密编织搭配顺滑的表面工艺,抛投时线阻更小,切水性更优秀。</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>SLN1010</v>
+        <v>SLN1025</v>
       </c>
       <c r="B59">
         <v>1</v>
       </c>
       <c r="C59" t="str">
-        <v>OCEA EX 前导线</v>
+        <v>SPINPOWER EX4</v>
       </c>
       <c r="D59" t="str">
-        <v/>
+        <v>SPINPOWER EX4</v>
       </c>
       <c r="E59" t="str">
         <v/>
@@ -2449,16 +2449,16 @@
         <v/>
       </c>
       <c r="G59" t="str">
-        <v>Fluorocarbon</v>
+        <v>PE</v>
       </c>
       <c r="H59" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%20EX%20%E5%89%8D%E5%AF%BC%E7%BA%BF_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/SPINPOWER%20EX4_main.jpeg</v>
       </c>
       <c r="I59" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J59" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K59" t="str">
         <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
@@ -2466,16 +2466,16 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>SLN1011</v>
+        <v>SLN1026</v>
       </c>
       <c r="B60">
         <v>1</v>
       </c>
       <c r="C60" t="str">
-        <v>LIMITED PRO G5+ PE</v>
+        <v>GRAPPLER 4</v>
       </c>
       <c r="D60" t="str">
-        <v/>
+        <v>GRAPPLER 4</v>
       </c>
       <c r="E60" t="str">
         <v/>
@@ -2487,30 +2487,30 @@
         <v>PE</v>
       </c>
       <c r="H60" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/LIMITED%20PRO%20G5%2B%20PE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/GRAPPLER%204_main.jpeg</v>
       </c>
       <c r="I60" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J60" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K60" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>入门~升级都能覆盖的船钓泛用PE线,原丝采用IZANAS高强度素材,和SHIMANO以往的4编PE线相比,有着更致密的编织构造,减少了渔线表面凹凸,提升了切水性能。关注渔线的伸度审计,具备一定缓冲性能有效防止切线,面对不经意的目标突袭也能更快反应,是一款非常容易使用的渔线。另外,采用了特殊硅涂层让渔线表面更顺滑,柔软特性能更好地融入水中,还采用了不易掉色的染色方法,追求高性价比的PE线。</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>SLN1012</v>
+        <v>SLN1027</v>
       </c>
       <c r="B61">
         <v>1</v>
       </c>
       <c r="C61" t="str">
-        <v>PITBULL 12</v>
+        <v>LAKEMASTER</v>
       </c>
       <c r="D61" t="str">
-        <v/>
+        <v>LAKEMASTER</v>
       </c>
       <c r="E61" t="str">
         <v/>
@@ -2522,30 +2522,30 @@
         <v>PE</v>
       </c>
       <c r="H61" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%2012_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/LAKEMASTER_main.jpeg</v>
       </c>
       <c r="I61" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J61" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K61" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>搭配渔轮Lake Master系列使用的渔线,主色使用白色更易识别,并且有线长标记。</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>SLN1013</v>
+        <v>SLN1028</v>
       </c>
       <c r="B62">
         <v>1</v>
       </c>
       <c r="C62" t="str">
-        <v>HARDBULL 8+</v>
+        <v>LIMITED PRO MASTER TOUGH-MUD</v>
       </c>
       <c r="D62" t="str">
-        <v/>
+        <v>LIMITED PRO MASTER TOUGH-MUD</v>
       </c>
       <c r="E62" t="str">
         <v/>
@@ -2554,16 +2554,16 @@
         <v/>
       </c>
       <c r="G62" t="str">
-        <v>PE</v>
+        <v>Fluorocarbon</v>
       </c>
       <c r="H62" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/HARDBULL%208%2B_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/LIMITED%20PRO%20MASTER%20TOUGH-MUD_main.jpeg</v>
       </c>
       <c r="I62" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J62" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K62" t="str">
         <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
@@ -2571,16 +2571,16 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>SLN1014</v>
+        <v>SLN1029</v>
       </c>
       <c r="B63">
         <v>1</v>
       </c>
       <c r="C63" t="str">
-        <v>GRAPPLER 8</v>
+        <v>LIMITED PRO MASTER</v>
       </c>
       <c r="D63" t="str">
-        <v/>
+        <v>LIMITED PRO MASTER</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2589,33 +2589,33 @@
         <v/>
       </c>
       <c r="G63" t="str">
-        <v>PE</v>
+        <v>Fluorocarbon</v>
       </c>
       <c r="H63" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/GRAPPLER%208_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/LIMITED%20PRO%20MASTER_main.jpeg</v>
       </c>
       <c r="I63" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J63" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K63" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>希望有一款能承受搭载CORE BLANKS技术矶竿的子线!为了响应这个呼声,我们采用高纯度氟碳素材,保证了直线强度和优秀的耐磨耗性能,在长时间使用后也不易掉色。从制法上看并不易实现,通过高纯度氟碳材质就可以让透明度和硬度保持平衡,另外我们采用柔软卷法让渔线保持了原有的特性。</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>SLN1015</v>
+        <v>SLN1030</v>
       </c>
       <c r="B64">
         <v>1</v>
       </c>
       <c r="C64" t="str">
-        <v>KISU SPECIAL EX4 13m</v>
+        <v>BB-X HYPER-REPEL α 漂浮</v>
       </c>
       <c r="D64" t="str">
-        <v/>
+        <v>BB-X HYPER-REPEL α 漂浮</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2624,16 +2624,16 @@
         <v/>
       </c>
       <c r="G64" t="str">
-        <v>PE</v>
+        <v>Nylon</v>
       </c>
       <c r="H64" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/KISU%20SPECIAL%20EX4%2013m_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BB-X%20HYPER-REPEL%20%CE%B1%20%E6%BC%82%E6%B5%AE_main.jpeg</v>
       </c>
       <c r="I64" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J64" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K64" t="str">
         <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
@@ -2641,16 +2641,16 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>SLN1016</v>
+        <v>SLN1031</v>
       </c>
       <c r="B65">
         <v>1</v>
       </c>
       <c r="C65" t="str">
-        <v>Tanatoru 4</v>
+        <v>BB-X PLASMA WHITE FLOAT</v>
       </c>
       <c r="D65" t="str">
-        <v/>
+        <v>BB-X PLASMA WHITE FLOAT</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2659,33 +2659,33 @@
         <v/>
       </c>
       <c r="G65" t="str">
-        <v>PE</v>
+        <v>Nylon</v>
       </c>
       <c r="H65" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Tanatoru%204%20_%208%20100m%20%20%E8%BF%9E%E7%9B%98_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BB-X%20PLASMA%20WHITE%20FLOAT_main.jpeg</v>
       </c>
       <c r="I65" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J65" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K65" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>当鱼所在水层较浅或风平浪静时,漂浮主线因其优异的操控性而格外受欢迎。BB-X PLASMA WHITE主线采用等离子表面处理,使其具备良好防泼水性能与浮力。非中空结构,采用实芯构造,拉伸强度提升8%,结节强度提升30%(与禧玛诺3号产品对比)。不会像传统涂层那样随着使用时间剥落,能长时间维持初始性能,让全天候垂钓体验更加轻松自在。</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>SLN1017</v>
+        <v>SLN1032</v>
       </c>
       <c r="B66">
         <v>1</v>
       </c>
       <c r="C66" t="str">
-        <v>KAIKON</v>
+        <v>PITBULL 4</v>
       </c>
       <c r="D66" t="str">
-        <v/>
+        <v>PITBULL 4</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2694,16 +2694,16 @@
         <v/>
       </c>
       <c r="G66" t="str">
-        <v>Nylon</v>
+        <v>PE</v>
       </c>
       <c r="H66" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/KAIKON_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%204_main.jpeg</v>
       </c>
       <c r="I66" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J66" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K66" t="str">
         <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
@@ -2711,16 +2711,16 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>SLN1018</v>
+        <v>SLN1033</v>
       </c>
       <c r="B67">
         <v>1</v>
       </c>
       <c r="C67" t="str">
-        <v>BULL'S EYE 远投</v>
+        <v>LIMITED PRO HYPER-REPEL α ZERO 漂浮</v>
       </c>
       <c r="D67" t="str">
-        <v/>
+        <v>LIMITED PRO HYPER-REPEL α ZERO 漂浮</v>
       </c>
       <c r="E67" t="str">
         <v/>
@@ -2732,13 +2732,13 @@
         <v>Nylon</v>
       </c>
       <c r="H67" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BULL'S%20EYE%20%E8%BF%9C%E6%8A%95_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/LIMITED%20PRO%20HYPER-REPEL%20%CE%B1%20ZERO%20%E6%BC%82%E6%B5%AE_main.jpeg</v>
       </c>
       <c r="I67" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J67" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K67" t="str">
         <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
@@ -2746,16 +2746,16 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>SLN1019</v>
+        <v>SLN1034</v>
       </c>
       <c r="B68">
         <v>1</v>
       </c>
       <c r="C68" t="str">
-        <v>OCEA JIGGER MASTER 前导线</v>
+        <v>LIMITED PRO 矶 ZERO 悬停 150m</v>
       </c>
       <c r="D68" t="str">
-        <v/>
+        <v>LIMITED PRO 矶 ZERO 悬停 150m</v>
       </c>
       <c r="E68" t="str">
         <v/>
@@ -2764,16 +2764,16 @@
         <v/>
       </c>
       <c r="G68" t="str">
-        <v>Fluorocarbon</v>
+        <v>Nylon</v>
       </c>
       <c r="H68" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%20JIGGER%20MASTER%20%E5%89%8D%E5%AF%BC%E7%BA%BF_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/LIMITED%20PRO%20%E7%9F%B6%20ZERO%20%E6%82%AC%E5%81%9C%20150m_main.jpeg</v>
       </c>
       <c r="I68" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J68" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K68" t="str">
         <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
@@ -2781,16 +2781,16 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>SLN1020</v>
+        <v>SLN1035</v>
       </c>
       <c r="B69">
         <v>1</v>
       </c>
       <c r="C69" t="str">
-        <v>Sephia 8+</v>
+        <v>BB-X PLASMA WHITE ZERO SUSPEND</v>
       </c>
       <c r="D69" t="str">
-        <v/>
+        <v>BB-X PLASMA WHITE ZERO SUSPEND</v>
       </c>
       <c r="E69" t="str">
         <v/>
@@ -2799,33 +2799,33 @@
         <v/>
       </c>
       <c r="G69" t="str">
-        <v>PE</v>
+        <v>Nylon</v>
       </c>
       <c r="H69" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Sephia%208%2B_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BB-X%20PLASMA%20WHITE%20ZERO%20SUSPEND_main.jpeg</v>
       </c>
       <c r="I69" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J69" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K69" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>随着垂钓时间延长,线的操控性变差的问题常常困扰钓友。BB-X PLASMA WHITE以出色的可视性和操控性缓解这一问题。非传统的表面涂层处理,而是采用PLASMA处理方式对表面分子进行化学改性,从源头延长初始性能,避免涂层脱落造成的防泼水性能下降。亚光白色的线体,在越细时反而越醒目。ZERO悬浮设计漂浮于海面以下,有效减轻风与表层洋流的影响,实现精准抛投与流放控制。</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>SLN1021</v>
+        <v>SLN1036</v>
       </c>
       <c r="B70">
         <v>1</v>
       </c>
       <c r="C70" t="str">
-        <v>PITBULL 8+</v>
+        <v>MASTIFF FC 90m</v>
       </c>
       <c r="D70" t="str">
-        <v/>
+        <v>MASTIFF FC 90m</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -2834,33 +2834,33 @@
         <v/>
       </c>
       <c r="G70" t="str">
-        <v>PE</v>
+        <v>Fluorocarbon</v>
       </c>
       <c r="H70" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%208%2B_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/MASTIFF%20FC%2090m_main.jpeg</v>
       </c>
       <c r="I70" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J70" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K70" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>追求路亚氟碳线所需要的性能。材质柔软表面顺滑,可以做到顺滑出线提升操作性。另外,在表面设置了纳米级凹凸的“NANOARMOR”构造,可以维持线结强度的氟碳线。和主线搭配,连接处不易打滑。</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>SLN1022</v>
+        <v>SLN1037</v>
       </c>
       <c r="B71">
         <v>1</v>
       </c>
       <c r="C71" t="str">
-        <v>FUKASE 船</v>
+        <v>OCEA 前导线</v>
       </c>
       <c r="D71" t="str">
-        <v/>
+        <v>OCEA 前导线</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -2869,33 +2869,33 @@
         <v/>
       </c>
       <c r="G71" t="str">
-        <v>Ester</v>
+        <v>Nylon</v>
       </c>
       <c r="H71" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/FUKASE%20%E8%88%B9_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%20%E5%89%8D%E5%AF%BC%E7%BA%BF_main.jpeg</v>
       </c>
       <c r="I71" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J71" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K71" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>尼龙线可以在有风不大的情况下能有效保持刚开始的伸度,在中鱼时减少力量损失。当要临近断线的时候线会适度延伸。使用高纯度材料维持了渔线的高透明性,白色是其特征。18号以上的粗线采用了特殊热处理技术,增加了柔软性,作为前导线在强力冲击下线也不容易散开。</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>SLN1023</v>
+        <v>SLN1038</v>
       </c>
       <c r="B72">
         <v>1</v>
       </c>
       <c r="C72" t="str">
-        <v>Sephia G5</v>
+        <v>FIREBLOOD HYPER-REPEL α ZERO 漂浮</v>
       </c>
       <c r="D72" t="str">
-        <v/>
+        <v>FIREBLOOD HYPER-REPEL α ZERO 漂浮</v>
       </c>
       <c r="E72" t="str">
         <v/>
@@ -2904,16 +2904,16 @@
         <v/>
       </c>
       <c r="G72" t="str">
-        <v>PE</v>
+        <v>Nylon</v>
       </c>
       <c r="H72" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Sephia%20G5_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/FIREBLOOD%20HYPER-REPEL%20%CE%B1%20ZERO%20%E6%BC%82%E6%B5%AE_main.jpeg</v>
       </c>
       <c r="I72" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J72" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K72" t="str">
         <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
@@ -2921,16 +2921,16 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>SLN1024</v>
+        <v>SLN1039</v>
       </c>
       <c r="B73">
         <v>1</v>
       </c>
       <c r="C73" t="str">
-        <v>Sephia 8</v>
+        <v>FIREBLOOD HYPER-REPEL α ZERO 悬停</v>
       </c>
       <c r="D73" t="str">
-        <v/>
+        <v>FIREBLOOD HYPER-REPEL α ZERO 悬停</v>
       </c>
       <c r="E73" t="str">
         <v/>
@@ -2939,16 +2939,16 @@
         <v/>
       </c>
       <c r="G73" t="str">
-        <v>PE</v>
+        <v>Nylon</v>
       </c>
       <c r="H73" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Sephia%208%2B_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/FIREBLOOD%20HYPER-REPEL%20%CE%B1%20ZERO%20%E6%82%AC%E5%81%9C_main.jpeg</v>
       </c>
       <c r="I73" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J73" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K73" t="str">
         <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
@@ -2956,16 +2956,16 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>SLN1025</v>
+        <v>SLN1040</v>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74" t="str">
-        <v>SPINPOWER EX4</v>
+        <v>BB-X HYPER-REPEL α 悬停</v>
       </c>
       <c r="D74" t="str">
-        <v/>
+        <v>BB-X HYPER-REPEL α 悬停</v>
       </c>
       <c r="E74" t="str">
         <v/>
@@ -2974,16 +2974,16 @@
         <v/>
       </c>
       <c r="G74" t="str">
-        <v>PE</v>
+        <v>Nylon</v>
       </c>
       <c r="H74" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/SPINPOWER%20EX4_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BB-X%20HYPER-REPEL%20%CE%B1%20%E6%82%AC%E5%81%9C_main.jpeg</v>
       </c>
       <c r="I74" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J74" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K74" t="str">
         <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
@@ -2991,16 +2991,16 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>SLN1026</v>
+        <v>SLN1041</v>
       </c>
       <c r="B75">
         <v>1</v>
       </c>
       <c r="C75" t="str">
-        <v>GRAPPLER 4</v>
+        <v>OCEA 16 30m</v>
       </c>
       <c r="D75" t="str">
-        <v/>
+        <v>OCEA 16 30m</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3012,30 +3012,30 @@
         <v>PE</v>
       </c>
       <c r="H75" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/GRAPPLER%204_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%2016%2030m_main.jpeg</v>
       </c>
       <c r="I75" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J75" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K75" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>保护抛投时容易受伤的打结位置,减少远投钓法的缠线问题。采用Spectra不畏惧强力冲击。</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>SLN1027</v>
+        <v>SLN1042</v>
       </c>
       <c r="B76">
         <v>1</v>
       </c>
       <c r="C76" t="str">
-        <v>LAKEMASTER</v>
+        <v>PITBULL 4+</v>
       </c>
       <c r="D76" t="str">
-        <v/>
+        <v>PITBULL 4+</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3047,30 +3047,30 @@
         <v>PE</v>
       </c>
       <c r="H76" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/LAKEMASTER_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%204%2B_main.jpeg</v>
       </c>
       <c r="I76" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J76" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K76" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>SHIMANO首次推出了极细规格PE线来对应路亚钓法啊,最细规格从0.15号开始。采用了特殊树脂涂层来提升顺滑性,让你更容易抛投轻量假饵。细腻咬讯也能传到手上,在管理钓场钓鳟鱼或竹荚鱼,另外溪流野钓都能发挥威力,颜色则采用了易识别的粉红色和灰色两种。</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>SLN1028</v>
+        <v>SLN1043</v>
       </c>
       <c r="B77">
         <v>1</v>
       </c>
       <c r="C77" t="str">
-        <v>LIMITED PRO MASTER TOUGH-MUD</v>
+        <v>BASIS G5 PE SUSPEND</v>
       </c>
       <c r="D77" t="str">
-        <v/>
+        <v>BASIS G5 PE SUSPEND</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3079,33 +3079,33 @@
         <v/>
       </c>
       <c r="G77" t="str">
-        <v>Fluorocarbon</v>
+        <v>PE</v>
       </c>
       <c r="H77" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/LIMITED%20PRO%20MASTER%20TOUGH-MUD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BASIS%20G5%20PE%20SUSPEND_main.jpeg</v>
       </c>
       <c r="I77" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J77" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K77" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>应对外海潮线、海底隆起等目标位置,当今的放流钓愈发重视“远投”这一关键点。此时,PE线就是强力武器。其直线强度约为尼龙的3倍,因此可使用更细的线号实现更远的抛投。且切水性优异,线控(mending)便捷,低延展性也有助于捕捉细微咬口。BASIS G5 PE悬停主线在单芯构造中加入了张力与比重设计,提升了耐久性。比重约为1.3的黄线在海面下漂浮,同时具备良好可视性,可减轻风与上滑潮的影响,实现精准控制。既然能轻松远投,更能轻松应对近距离作钓。通过合理定价,让更多钓友轻松体验PE线的优势与乐趣。</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>SLN1029</v>
+        <v>SLN1044</v>
       </c>
       <c r="B78">
         <v>1</v>
       </c>
       <c r="C78" t="str">
-        <v>LIMITED PRO MASTER</v>
+        <v>FIREBLOOD STRETCH 悬停</v>
       </c>
       <c r="D78" t="str">
-        <v/>
+        <v>FIREBLOOD STRETCH 悬停</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3114,16 +3114,16 @@
         <v/>
       </c>
       <c r="G78" t="str">
-        <v>Fluorocarbon</v>
+        <v>Nylon</v>
       </c>
       <c r="H78" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/LIMITED%20PRO%20MASTER%20TOUGH-MUD_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/FIREBLOOD%20STRETCH%20%E6%82%AC%E5%81%9C_main.jpeg</v>
       </c>
       <c r="I78" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J78" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K78" t="str">
         <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
@@ -3131,16 +3131,16 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>SLN1030</v>
+        <v>SLN1045</v>
       </c>
       <c r="B79">
         <v>1</v>
       </c>
       <c r="C79" t="str">
-        <v>BB-X HYPER-REPEL α 漂浮</v>
+        <v>SIGHT LASER EX 240m</v>
       </c>
       <c r="D79" t="str">
-        <v/>
+        <v>SIGHT LASER EX 240m</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3149,33 +3149,33 @@
         <v/>
       </c>
       <c r="G79" t="str">
-        <v>Nylon</v>
+        <v>Ester</v>
       </c>
       <c r="H79" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BB-X%20HYPER-REPEL%20%CE%B1%20%E6%BC%82%E6%B5%AE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/SIGHT%20LASER%20EX%20240m_main.jpeg</v>
       </c>
       <c r="I79" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J79" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K79" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>溶水性好,适合用小型亮片或铅头钩这种轻量假饵。另外,在强风等恶劣条件时也容易控制。为了确认线以及方便操控,我们采用了加强识别性的颜色。新的颜色还追加了高识别性的荧光绿,通过追加不同号数和颜色也让线的功能性更丰富。聚酯纤维的素材特性,容易有收线记忆,使用时依靠张力,让延展性发挥出来。在增加直进性后,让你更容易感知咬讯。</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>SLN1031</v>
+        <v>SLN1046</v>
       </c>
       <c r="B80">
         <v>1</v>
       </c>
       <c r="C80" t="str">
-        <v>BB-X PLASMA WHITE FLOAT</v>
+        <v>PITBULL G5</v>
       </c>
       <c r="D80" t="str">
-        <v/>
+        <v>PITBULL G5</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3184,16 +3184,16 @@
         <v/>
       </c>
       <c r="G80" t="str">
-        <v>Nylon</v>
+        <v>PE</v>
       </c>
       <c r="H80" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BB-X%20PLASMA%20WHITE%20FLOAT_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%20G5_main.jpeg</v>
       </c>
       <c r="I80" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J80" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K80" t="str">
         <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
@@ -3201,16 +3201,16 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>SLN1032</v>
+        <v>SLN1047</v>
       </c>
       <c r="B81">
         <v>1</v>
       </c>
       <c r="C81" t="str">
-        <v>PITBULL 4</v>
+        <v>Soare AJING 150m</v>
       </c>
       <c r="D81" t="str">
-        <v/>
+        <v>Soare AJING 150m</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3219,16 +3219,16 @@
         <v/>
       </c>
       <c r="G81" t="str">
-        <v>PE</v>
+        <v>Fluorocarbon</v>
       </c>
       <c r="H81" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%204%2B_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Soare%20AJING%20150m_main.jpeg</v>
       </c>
       <c r="I81" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J81" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K81" t="str">
         <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
@@ -3236,16 +3236,16 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>SLN1033</v>
+        <v>SLN1048</v>
       </c>
       <c r="B82">
         <v>1</v>
       </c>
       <c r="C82" t="str">
-        <v>LIMITED PRO HYPER-REPEL α ZERO 漂浮</v>
+        <v>Sephia MASTER 前导线 30m</v>
       </c>
       <c r="D82" t="str">
-        <v/>
+        <v>Sephia MASTER 前导线 30m</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3254,33 +3254,33 @@
         <v/>
       </c>
       <c r="G82" t="str">
-        <v>Nylon</v>
+        <v>Fluorocarbon</v>
       </c>
       <c r="H82" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/LIMITED%20PRO%20HYPER-REPEL%20%CE%B1%20ZERO%20%E6%BC%82%E6%B5%AE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Sephia%20MASTER%20%E5%89%8D%E5%AF%BC%E7%BA%BF%2030m_main.jpeg</v>
       </c>
       <c r="I82" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J82" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K82" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>采用MasterFluoro!作为构造单位,使用的树脂分子量越多,打结强度就越高。两重断面构造。直线强度和打结强度兼顾,打结后能牢牢固定。柔软型规格编制线的过程中采用了弹性工程。柔软风格让木虾假饵更贴合海浪,表面平滑的样式让透明度也有所提升。</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>SLN1034</v>
+        <v>SLN1049</v>
       </c>
       <c r="B83">
         <v>1</v>
       </c>
       <c r="C83" t="str">
-        <v>LIMITED PRO 矶 ZERO 悬停 150m</v>
+        <v>BB BRAID</v>
       </c>
       <c r="D83" t="str">
-        <v/>
+        <v>BB BRAID</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3289,33 +3289,33 @@
         <v/>
       </c>
       <c r="G83" t="str">
-        <v>Nylon</v>
+        <v>PE</v>
       </c>
       <c r="H83" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/LIMITED%20PRO%20%E7%9F%B6%20ZERO%20%E6%82%AC%E5%81%9C%20150m_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BB%20BRAID_main.jpeg</v>
       </c>
       <c r="I83" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J83" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K83" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>在保持必要的强度和耐久性的同时,有着高性价比的日产PE线。不仅是入门者,也很适合替换渔线频繁的老手。</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>SLN1035</v>
+        <v>SLN1050</v>
       </c>
       <c r="B84">
         <v>1</v>
       </c>
       <c r="C84" t="str">
-        <v>BB-X PLASMA WHITE ZERO SUSPEND</v>
+        <v>BAISIS 矶</v>
       </c>
       <c r="D84" t="str">
-        <v/>
+        <v>BAISIS 矶</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3327,13 +3327,13 @@
         <v>Nylon</v>
       </c>
       <c r="H84" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BB-X%20PLASMA%20WHITE%20ZERO%20SUSPEND_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BAISIS%20%E7%9F%B6_main.jpeg</v>
       </c>
       <c r="I84" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J84" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K84" t="str">
         <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
@@ -3341,16 +3341,16 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>SLN1036</v>
+        <v>SLN1051</v>
       </c>
       <c r="B85">
         <v>1</v>
       </c>
       <c r="C85" t="str">
-        <v>MASTIFF FC 90m</v>
+        <v>BASIS ORANGE ZERO SUSPEND</v>
       </c>
       <c r="D85" t="str">
-        <v/>
+        <v>BASIS ORANGE ZERO SUSPEND</v>
       </c>
       <c r="E85" t="str">
         <v/>
@@ -3359,33 +3359,33 @@
         <v/>
       </c>
       <c r="G85" t="str">
-        <v>Fluorocarbon</v>
+        <v>Nylon</v>
       </c>
       <c r="H85" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/MASTIFF%20FC%2090m_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BASIS%20ORANGE%20ZERO%20SUSPEND_main.jpeg</v>
       </c>
       <c r="I85" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J85" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K85" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>在潮水中放流钓组时,主线的放置与控制极为关键。若主线膨胀至浮漂前方、拉力过强或过松,钓组便无法顺利沉降,容易偏离目标水层,进而影响渔获。BASIS ORANGE ZERO采用极具可视性的橙色,漂浮于海面以下,有助于精准操控道线并顺利引导钓饵接近鱼口。提供1.5、1.75、2.0、2.5/3.0/4.0、5.0/6.0号等5个段位,针对不同粗细进行硬度与手感调校:线径越细越硬,越粗则越柔软,确保舒适操控性。</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>SLN1037</v>
+        <v>SLN1052</v>
       </c>
       <c r="B86">
         <v>1</v>
       </c>
       <c r="C86" t="str">
-        <v>OCEA 前导线</v>
+        <v>BAISIS EX</v>
       </c>
       <c r="D86" t="str">
-        <v/>
+        <v>BAISIS EX</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3394,16 +3394,16 @@
         <v/>
       </c>
       <c r="G86" t="str">
-        <v>Nylon</v>
+        <v>Fluorocarbon</v>
       </c>
       <c r="H86" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%20%E5%89%8D%E5%AF%BC%E7%BA%BF_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BAISIS%20EX_main.jpeg</v>
       </c>
       <c r="I86" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J86" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K86" t="str">
         <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
@@ -3411,16 +3411,16 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>SLN1038</v>
+        <v>SLN1053</v>
       </c>
       <c r="B87">
         <v>1</v>
       </c>
       <c r="C87" t="str">
-        <v>FIREBLOOD HYPER-REPEL α ZERO 漂浮</v>
+        <v>EXSENCE 前导线 EX 30m</v>
       </c>
       <c r="D87" t="str">
-        <v/>
+        <v>EXSENCE 前导线 EX 30m</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3429,16 +3429,16 @@
         <v/>
       </c>
       <c r="G87" t="str">
-        <v>Nylon</v>
+        <v>Fluorocarbon</v>
       </c>
       <c r="H87" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/FIREBLOOD%20HYPER-REPEL%20%CE%B1%20ZERO%20%E6%BC%82%E6%B5%AE_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/EXSENCE%20%E5%89%8D%E5%AF%BC%E7%BA%BF%20EX%2030m_main.jpeg</v>
       </c>
       <c r="I87" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J87" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K87" t="str">
         <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
@@ -3446,16 +3446,16 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>SLN1039</v>
+        <v>SLN1054</v>
       </c>
       <c r="B88">
         <v>1</v>
       </c>
       <c r="C88" t="str">
-        <v>FIREBLOOD HYPER-REPEL α ZERO 悬停</v>
+        <v>炎月 EX 前导线 30m</v>
       </c>
       <c r="D88" t="str">
-        <v/>
+        <v>炎月 EX 前导线 30m</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3464,16 +3464,16 @@
         <v/>
       </c>
       <c r="G88" t="str">
-        <v>Nylon</v>
+        <v>Fluorocarbon</v>
       </c>
       <c r="H88" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/FIREBLOOD%20HYPER-REPEL%20%CE%B1%20ZERO%20%E6%82%AC%E5%81%9C_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/%E7%82%8E%E6%9C%88%20EX%20%E5%89%8D%E5%AF%BC%E7%BA%BF%2030m_main.jpeg</v>
       </c>
       <c r="I88" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J88" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K88" t="str">
         <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
@@ -3481,16 +3481,16 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>SLN1040</v>
+        <v>SLN1055</v>
       </c>
       <c r="B89">
         <v>1</v>
       </c>
       <c r="C89" t="str">
-        <v>BB-X HYPER-REPEL α 悬停</v>
+        <v>Soare 前导线 EX 30m</v>
       </c>
       <c r="D89" t="str">
-        <v/>
+        <v>Soare 前导线 EX 30m</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3499,16 +3499,16 @@
         <v/>
       </c>
       <c r="G89" t="str">
-        <v>Nylon</v>
+        <v>Fluorocarbon</v>
       </c>
       <c r="H89" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BB-X%20HYPER-REPEL%20%CE%B1%20%E6%82%AC%E5%81%9C_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Soare%20%E5%89%8D%E5%AF%BC%E7%BA%BF%20EX%2030m_main.jpeg</v>
       </c>
       <c r="I89" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J89" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K89" t="str">
         <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
@@ -3516,16 +3516,16 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>SLN1041</v>
+        <v>SLN1056</v>
       </c>
       <c r="B90">
         <v>1</v>
       </c>
       <c r="C90" t="str">
-        <v>OCEA 16 30m</v>
+        <v>Sephia 前导线 30m</v>
       </c>
       <c r="D90" t="str">
-        <v/>
+        <v>Sephia 前导线 30m</v>
       </c>
       <c r="E90" t="str">
         <v/>
@@ -3534,33 +3534,33 @@
         <v/>
       </c>
       <c r="G90" t="str">
-        <v>PE</v>
+        <v>Fluorocarbon</v>
       </c>
       <c r="H90" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/OCEA%2016%2030m_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Sephia%20%E5%89%8D%E5%AF%BC%E7%BA%BF%2030m_main.jpeg</v>
       </c>
       <c r="I90" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J90" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K90" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
+        <v>采用EX FLUORO!采用新的氟碳材质后,直线/结节强度比旧款又有了提升。Hyper Repel涂层表面采用硅树脂涂层提升了水溶性。让带钩子的木虾假饵跳跃性能上升,力量更容易传达到假饵上,提升直进性。</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>SLN1042</v>
+        <v>SLN1057</v>
       </c>
       <c r="B91">
         <v>1</v>
       </c>
       <c r="C91" t="str">
-        <v>PITBULL 4+</v>
+        <v>LIMITED PRO 前导线 悬停</v>
       </c>
       <c r="D91" t="str">
-        <v/>
+        <v>LIMITED PRO 前导线 悬停</v>
       </c>
       <c r="E91" t="str">
         <v/>
@@ -3569,16 +3569,16 @@
         <v/>
       </c>
       <c r="G91" t="str">
-        <v>PE</v>
+        <v>Nylon</v>
       </c>
       <c r="H91" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%204%2B_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/LIMITED%20PRO%20%E5%89%8D%E5%AF%BC%E7%BA%BF%20%E6%82%AC%E5%81%9C_main.jpeg</v>
       </c>
       <c r="I91" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J91" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K91" t="str">
         <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
@@ -3586,16 +3586,16 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>SLN1043</v>
+        <v>SLN1058</v>
       </c>
       <c r="B92">
         <v>1</v>
       </c>
       <c r="C92" t="str">
-        <v>BASIS G5 PE SUSPEND</v>
+        <v>PITBULL 8</v>
       </c>
       <c r="D92" t="str">
-        <v/>
+        <v>PITBULL 8</v>
       </c>
       <c r="E92" t="str">
         <v/>
@@ -3607,546 +3607,21 @@
         <v>PE</v>
       </c>
       <c r="H92" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BASIS%20G5%20PE%20SUSPEND_main.jpg</v>
+        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%208_main.jpeg</v>
       </c>
       <c r="I92" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="J92" t="str">
-        <v/>
+        <v>2026-05-02 09:13:28</v>
       </c>
       <c r="K92" t="str">
         <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="str">
-        <v>SLN1044</v>
-      </c>
-      <c r="B93">
-        <v>1</v>
-      </c>
-      <c r="C93" t="str">
-        <v>FIREBLOOD STRETCH 悬停</v>
-      </c>
-      <c r="D93" t="str">
-        <v/>
-      </c>
-      <c r="E93" t="str">
-        <v/>
-      </c>
-      <c r="F93" t="str">
-        <v/>
-      </c>
-      <c r="G93" t="str">
-        <v>Nylon</v>
-      </c>
-      <c r="H93" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/FIREBLOOD%20STRETCH%20%E6%82%AC%E5%81%9C_main.jpg</v>
-      </c>
-      <c r="I93" t="str">
-        <v/>
-      </c>
-      <c r="J93" t="str">
-        <v/>
-      </c>
-      <c r="K93" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="str">
-        <v>SLN1045</v>
-      </c>
-      <c r="B94">
-        <v>1</v>
-      </c>
-      <c r="C94" t="str">
-        <v>SIGHT LASER EX 240m</v>
-      </c>
-      <c r="D94" t="str">
-        <v/>
-      </c>
-      <c r="E94" t="str">
-        <v/>
-      </c>
-      <c r="F94" t="str">
-        <v/>
-      </c>
-      <c r="G94" t="str">
-        <v>Ester</v>
-      </c>
-      <c r="H94" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/SIGHT%20LASER%20EX%20240m_main.jpg</v>
-      </c>
-      <c r="I94" t="str">
-        <v/>
-      </c>
-      <c r="J94" t="str">
-        <v/>
-      </c>
-      <c r="K94" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="str">
-        <v>SLN1046</v>
-      </c>
-      <c r="B95">
-        <v>1</v>
-      </c>
-      <c r="C95" t="str">
-        <v>PITBULL G5</v>
-      </c>
-      <c r="D95" t="str">
-        <v/>
-      </c>
-      <c r="E95" t="str">
-        <v/>
-      </c>
-      <c r="F95" t="str">
-        <v/>
-      </c>
-      <c r="G95" t="str">
-        <v>PE</v>
-      </c>
-      <c r="H95" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%20G5_main.jpg</v>
-      </c>
-      <c r="I95" t="str">
-        <v/>
-      </c>
-      <c r="J95" t="str">
-        <v/>
-      </c>
-      <c r="K95" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="str">
-        <v>SLN1047</v>
-      </c>
-      <c r="B96">
-        <v>1</v>
-      </c>
-      <c r="C96" t="str">
-        <v>Soare AJING 150m</v>
-      </c>
-      <c r="D96" t="str">
-        <v/>
-      </c>
-      <c r="E96" t="str">
-        <v/>
-      </c>
-      <c r="F96" t="str">
-        <v/>
-      </c>
-      <c r="G96" t="str">
-        <v>Fluorocarbon</v>
-      </c>
-      <c r="H96" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Soare%20AJING%20150m_main.jpg</v>
-      </c>
-      <c r="I96" t="str">
-        <v/>
-      </c>
-      <c r="J96" t="str">
-        <v/>
-      </c>
-      <c r="K96" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="str">
-        <v>SLN1048</v>
-      </c>
-      <c r="B97">
-        <v>1</v>
-      </c>
-      <c r="C97" t="str">
-        <v>Sephia MASTER 前导线 30m</v>
-      </c>
-      <c r="D97" t="str">
-        <v/>
-      </c>
-      <c r="E97" t="str">
-        <v/>
-      </c>
-      <c r="F97" t="str">
-        <v/>
-      </c>
-      <c r="G97" t="str">
-        <v>Fluorocarbon</v>
-      </c>
-      <c r="H97" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Sephia%20MASTER%20%E5%89%8D%E5%AF%BC%E7%BA%BF%2030m_main.jpg</v>
-      </c>
-      <c r="I97" t="str">
-        <v/>
-      </c>
-      <c r="J97" t="str">
-        <v/>
-      </c>
-      <c r="K97" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="str">
-        <v>SLN1049</v>
-      </c>
-      <c r="B98">
-        <v>1</v>
-      </c>
-      <c r="C98" t="str">
-        <v>BB BRAID</v>
-      </c>
-      <c r="D98" t="str">
-        <v/>
-      </c>
-      <c r="E98" t="str">
-        <v/>
-      </c>
-      <c r="F98" t="str">
-        <v/>
-      </c>
-      <c r="G98" t="str">
-        <v>PE</v>
-      </c>
-      <c r="H98" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BB%20BRAID_main.jpg</v>
-      </c>
-      <c r="I98" t="str">
-        <v/>
-      </c>
-      <c r="J98" t="str">
-        <v/>
-      </c>
-      <c r="K98" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="str">
-        <v>SLN1050</v>
-      </c>
-      <c r="B99">
-        <v>1</v>
-      </c>
-      <c r="C99" t="str">
-        <v>BAISIS 矶</v>
-      </c>
-      <c r="D99" t="str">
-        <v/>
-      </c>
-      <c r="E99" t="str">
-        <v/>
-      </c>
-      <c r="F99" t="str">
-        <v/>
-      </c>
-      <c r="G99" t="str">
-        <v>Nylon</v>
-      </c>
-      <c r="H99" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BAISIS%20%E7%9F%B6_main.jpg</v>
-      </c>
-      <c r="I99" t="str">
-        <v/>
-      </c>
-      <c r="J99" t="str">
-        <v/>
-      </c>
-      <c r="K99" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="str">
-        <v>SLN1051</v>
-      </c>
-      <c r="B100">
-        <v>1</v>
-      </c>
-      <c r="C100" t="str">
-        <v>BASIS ORANGE ZERO SUSPEND</v>
-      </c>
-      <c r="D100" t="str">
-        <v/>
-      </c>
-      <c r="E100" t="str">
-        <v/>
-      </c>
-      <c r="F100" t="str">
-        <v/>
-      </c>
-      <c r="G100" t="str">
-        <v>Nylon</v>
-      </c>
-      <c r="H100" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BASIS%20ORANGE%20ZERO%20SUSPEND_main.jpg</v>
-      </c>
-      <c r="I100" t="str">
-        <v/>
-      </c>
-      <c r="J100" t="str">
-        <v/>
-      </c>
-      <c r="K100" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="str">
-        <v>SLN1052</v>
-      </c>
-      <c r="B101">
-        <v>1</v>
-      </c>
-      <c r="C101" t="str">
-        <v>BAISIS EX</v>
-      </c>
-      <c r="D101" t="str">
-        <v/>
-      </c>
-      <c r="E101" t="str">
-        <v/>
-      </c>
-      <c r="F101" t="str">
-        <v/>
-      </c>
-      <c r="G101" t="str">
-        <v>Fluorocarbon</v>
-      </c>
-      <c r="H101" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/BAISIS%20EX_main.jpg</v>
-      </c>
-      <c r="I101" t="str">
-        <v/>
-      </c>
-      <c r="J101" t="str">
-        <v/>
-      </c>
-      <c r="K101" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="str">
-        <v>SLN1053</v>
-      </c>
-      <c r="B102">
-        <v>1</v>
-      </c>
-      <c r="C102" t="str">
-        <v>EXSENCE 前导线 EX 30m</v>
-      </c>
-      <c r="D102" t="str">
-        <v/>
-      </c>
-      <c r="E102" t="str">
-        <v/>
-      </c>
-      <c r="F102" t="str">
-        <v/>
-      </c>
-      <c r="G102" t="str">
-        <v>Fluorocarbon</v>
-      </c>
-      <c r="H102" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/EXSENCE%20%E5%89%8D%E5%AF%BC%E7%BA%BF%20EX%2030m_main.jpg</v>
-      </c>
-      <c r="I102" t="str">
-        <v/>
-      </c>
-      <c r="J102" t="str">
-        <v/>
-      </c>
-      <c r="K102" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="str">
-        <v>SLN1054</v>
-      </c>
-      <c r="B103">
-        <v>1</v>
-      </c>
-      <c r="C103" t="str">
-        <v>炎月 EX 前导线 30m</v>
-      </c>
-      <c r="D103" t="str">
-        <v/>
-      </c>
-      <c r="E103" t="str">
-        <v/>
-      </c>
-      <c r="F103" t="str">
-        <v/>
-      </c>
-      <c r="G103" t="str">
-        <v>Fluorocarbon</v>
-      </c>
-      <c r="H103" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/%E7%82%8E%E6%9C%88%20EX%20%E5%89%8D%E5%AF%BC%E7%BA%BF%2030m_main.jpg</v>
-      </c>
-      <c r="I103" t="str">
-        <v/>
-      </c>
-      <c r="J103" t="str">
-        <v/>
-      </c>
-      <c r="K103" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="str">
-        <v>SLN1055</v>
-      </c>
-      <c r="B104">
-        <v>1</v>
-      </c>
-      <c r="C104" t="str">
-        <v>Soare 前导线 EX 30m</v>
-      </c>
-      <c r="D104" t="str">
-        <v/>
-      </c>
-      <c r="E104" t="str">
-        <v/>
-      </c>
-      <c r="F104" t="str">
-        <v/>
-      </c>
-      <c r="G104" t="str">
-        <v>Fluorocarbon</v>
-      </c>
-      <c r="H104" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Soare%20%E5%89%8D%E5%AF%BC%E7%BA%BF%20EX%2030m_main.jpg</v>
-      </c>
-      <c r="I104" t="str">
-        <v/>
-      </c>
-      <c r="J104" t="str">
-        <v/>
-      </c>
-      <c r="K104" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="str">
-        <v>SLN1056</v>
-      </c>
-      <c r="B105">
-        <v>1</v>
-      </c>
-      <c r="C105" t="str">
-        <v>Sephia 前导线 30m</v>
-      </c>
-      <c r="D105" t="str">
-        <v/>
-      </c>
-      <c r="E105" t="str">
-        <v/>
-      </c>
-      <c r="F105" t="str">
-        <v/>
-      </c>
-      <c r="G105" t="str">
-        <v>Fluorocarbon</v>
-      </c>
-      <c r="H105" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/Sephia%20%E5%89%8D%E5%AF%BC%E7%BA%BF%2030m_main.jpg</v>
-      </c>
-      <c r="I105" t="str">
-        <v/>
-      </c>
-      <c r="J105" t="str">
-        <v/>
-      </c>
-      <c r="K105" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="str">
-        <v>SLN1057</v>
-      </c>
-      <c r="B106">
-        <v>1</v>
-      </c>
-      <c r="C106" t="str">
-        <v>LIMITED PRO 前导线 悬停</v>
-      </c>
-      <c r="D106" t="str">
-        <v/>
-      </c>
-      <c r="E106" t="str">
-        <v/>
-      </c>
-      <c r="F106" t="str">
-        <v/>
-      </c>
-      <c r="G106" t="str">
-        <v>Nylon</v>
-      </c>
-      <c r="H106" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/LIMITED%20PRO%20%E5%89%8D%E5%AF%BC%E7%BA%BF%20%E6%82%AC%E5%81%9C_main.jpg</v>
-      </c>
-      <c r="I106" t="str">
-        <v/>
-      </c>
-      <c r="J106" t="str">
-        <v/>
-      </c>
-      <c r="K106" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="str">
-        <v>SLN1058</v>
-      </c>
-      <c r="B107">
-        <v>1</v>
-      </c>
-      <c r="C107" t="str">
-        <v>PITBULL 8</v>
-      </c>
-      <c r="D107" t="str">
-        <v/>
-      </c>
-      <c r="E107" t="str">
-        <v/>
-      </c>
-      <c r="F107" t="str">
-        <v/>
-      </c>
-      <c r="G107" t="str">
-        <v>PE</v>
-      </c>
-      <c r="H107" t="str">
-        <v>https://static.gearsage.club/gearsage/Gearimg/images/shimano_lines/PITBULL%208%2B_main.jpg</v>
-      </c>
-      <c r="I107" t="str">
-        <v/>
-      </c>
-      <c r="J107" t="str">
-        <v/>
-      </c>
-      <c r="K107" t="str">
-        <v>※本页面相关产品数据为禧玛诺自身产品对比，内部测试所得。</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K107"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K92"/>
   </ignoredErrors>
 </worksheet>
 </file>